--- a/data/kamper_2026.xlsx
+++ b/data/kamper_2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
   <si>
     <t>Runde</t>
   </si>
@@ -119,6 +119,36 @@
     <t>17:00</t>
   </si>
   <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>1 - 0</t>
+  </si>
+  <si>
+    <t>Sandefjord Fotball</t>
+  </si>
+  <si>
+    <t>Intility Arena</t>
+  </si>
+  <si>
+    <t>99120001007</t>
+  </si>
+  <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>1 - 3</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Color Line Stadion</t>
+  </si>
+  <si>
+    <t>99120001008</t>
+  </si>
+  <si>
     <t>KFUM</t>
   </si>
   <si>
@@ -131,36 +161,6 @@
     <t>99120001002</t>
   </si>
   <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>1 - 3</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Color Line Stadion</t>
-  </si>
-  <si>
-    <t>99120001008</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
-    <t>1 - 0</t>
-  </si>
-  <si>
-    <t>Sandefjord Fotball</t>
-  </si>
-  <si>
-    <t>Intility Arena</t>
-  </si>
-  <si>
-    <t>99120001007</t>
-  </si>
-  <si>
     <t>19:15</t>
   </si>
   <si>
@@ -368,12 +368,12 @@
     <t>99120001037</t>
   </si>
   <si>
+    <t>99120001035</t>
+  </si>
+  <si>
     <t>99120001034</t>
   </si>
   <si>
-    <t>99120001035</t>
-  </si>
-  <si>
     <t>99120001038</t>
   </si>
   <si>
@@ -392,12 +392,12 @@
     <t>99120001045</t>
   </si>
   <si>
+    <t>99120001047</t>
+  </si>
+  <si>
     <t>99120001048</t>
   </si>
   <si>
-    <t>99120001047</t>
-  </si>
-  <si>
     <t>99120001042</t>
   </si>
   <si>
@@ -425,12 +425,12 @@
     <t>99120001051</t>
   </si>
   <si>
+    <t>99120001053</t>
+  </si>
+  <si>
     <t>99120001054</t>
   </si>
   <si>
-    <t>99120001053</t>
-  </si>
-  <si>
     <t>99120001056</t>
   </si>
   <si>
@@ -449,12 +449,12 @@
     <t>99120001059</t>
   </si>
   <si>
+    <t>99120001060</t>
+  </si>
+  <si>
     <t>99120001063</t>
   </si>
   <si>
-    <t>99120001060</t>
-  </si>
-  <si>
     <t>99120001058</t>
   </si>
   <si>
@@ -476,24 +476,24 @@
     <t>99120001066</t>
   </si>
   <si>
+    <t>99120001068</t>
+  </si>
+  <si>
     <t>99120001070</t>
   </si>
   <si>
-    <t>99120001068</t>
+    <t>99120001069</t>
+  </si>
+  <si>
+    <t>6 - 3</t>
+  </si>
+  <si>
+    <t>99120001071</t>
   </si>
   <si>
     <t>99120001067</t>
   </si>
   <si>
-    <t>99120001069</t>
-  </si>
-  <si>
-    <t>6 - 3</t>
-  </si>
-  <si>
-    <t>99120001071</t>
-  </si>
-  <si>
     <t>99120001065</t>
   </si>
   <si>
@@ -530,24 +530,24 @@
     <t>11</t>
   </si>
   <si>
+    <t>99120001087</t>
+  </si>
+  <si>
     <t>99120001081</t>
   </si>
   <si>
-    <t>99120001087</t>
-  </si>
-  <si>
     <t>99120001082</t>
   </si>
   <si>
+    <t>99120001086</t>
+  </si>
+  <si>
+    <t>99120001088</t>
+  </si>
+  <si>
     <t>99120001083</t>
   </si>
   <si>
-    <t>99120001086</t>
-  </si>
-  <si>
-    <t>99120001088</t>
-  </si>
-  <si>
     <t>99120001085</t>
   </si>
   <si>
@@ -560,18 +560,18 @@
     <t>-</t>
   </si>
   <si>
+    <t>99120001092</t>
+  </si>
+  <si>
+    <t>99120001095</t>
+  </si>
+  <si>
+    <t>99120001096</t>
+  </si>
+  <si>
     <t>99120001091</t>
   </si>
   <si>
-    <t>99120001092</t>
-  </si>
-  <si>
-    <t>99120001096</t>
-  </si>
-  <si>
-    <t>99120001095</t>
-  </si>
-  <si>
     <t>99120001089</t>
   </si>
   <si>
@@ -629,12 +629,12 @@
     <t>99120001106</t>
   </si>
   <si>
+    <t>99120001110</t>
+  </si>
+  <si>
     <t>99120001108</t>
   </si>
   <si>
-    <t>99120001110</t>
-  </si>
-  <si>
     <t>99120001107</t>
   </si>
   <si>
@@ -656,6 +656,9 @@
     <t>99120001113</t>
   </si>
   <si>
+    <t>99120001117</t>
+  </si>
+  <si>
     <t>99120001118</t>
   </si>
   <si>
@@ -665,9 +668,6 @@
     <t>99120001114</t>
   </si>
   <si>
-    <t>99120001117</t>
-  </si>
-  <si>
     <t>99120001120</t>
   </si>
   <si>
@@ -692,10 +692,16 @@
     <t>99120001126</t>
   </si>
   <si>
+    <t>3 - 3</t>
+  </si>
+  <si>
+    <t>99120001125</t>
+  </si>
+  <si>
     <t>99120001124</t>
   </si>
   <si>
-    <t>99120001125</t>
+    <t>2 - 6</t>
   </si>
   <si>
     <t>99120001128</t>
@@ -746,6 +752,9 @@
     <t>99120001140</t>
   </si>
   <si>
+    <t>5 - 5</t>
+  </si>
+  <si>
     <t>99120001144</t>
   </si>
   <si>
@@ -764,39 +773,45 @@
     <t>19</t>
   </si>
   <si>
+    <t>4 - 2</t>
+  </si>
+  <si>
+    <t>99120001145</t>
+  </si>
+  <si>
+    <t>99120001146</t>
+  </si>
+  <si>
+    <t>99120001148</t>
+  </si>
+  <si>
+    <t>99120001150</t>
+  </si>
+  <si>
+    <t>99120001149</t>
+  </si>
+  <si>
+    <t>99120001151</t>
+  </si>
+  <si>
+    <t>3 - 4</t>
+  </si>
+  <si>
     <t>99120001152</t>
   </si>
   <si>
-    <t>99120001151</t>
-  </si>
-  <si>
-    <t>99120001145</t>
-  </si>
-  <si>
-    <t>99120001146</t>
-  </si>
-  <si>
-    <t>99120001149</t>
-  </si>
-  <si>
-    <t>99120001150</t>
-  </si>
-  <si>
-    <t>99120001148</t>
-  </si>
-  <si>
     <t>99120001147</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
+    <t>99120001160</t>
+  </si>
+  <si>
     <t>99120001154</t>
   </si>
   <si>
-    <t>99120001160</t>
-  </si>
-  <si>
     <t>99120001158</t>
   </si>
   <si>
@@ -806,15 +821,15 @@
     <t>99120001153</t>
   </si>
   <si>
+    <t>99120001159</t>
+  </si>
+  <si>
     <t>99120001156</t>
   </si>
   <si>
     <t>99120001155</t>
   </si>
   <si>
-    <t>99120001159</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
@@ -833,12 +848,12 @@
     <t>99120001167</t>
   </si>
   <si>
+    <t>99120001161</t>
+  </si>
+  <si>
     <t>99120001163</t>
   </si>
   <si>
-    <t>99120001161</t>
-  </si>
-  <si>
     <t>99120001162</t>
   </si>
   <si>
@@ -857,15 +872,15 @@
     <t>99120001176</t>
   </si>
   <si>
+    <t>99120001172</t>
+  </si>
+  <si>
     <t>99120001174</t>
   </si>
   <si>
     <t>99120001175</t>
   </si>
   <si>
-    <t>99120001172</t>
-  </si>
-  <si>
     <t>99120001169</t>
   </si>
   <si>
@@ -887,42 +902,42 @@
     <t>99120001179</t>
   </si>
   <si>
+    <t>99120001182</t>
+  </si>
+  <si>
     <t>99120001183</t>
   </si>
   <si>
     <t>99120001184</t>
   </si>
   <si>
-    <t>99120001182</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
     <t>99120001186</t>
   </si>
   <si>
+    <t>99120001192</t>
+  </si>
+  <si>
     <t>99120001189</t>
   </si>
   <si>
-    <t>99120001192</t>
-  </si>
-  <si>
     <t>99120001185</t>
   </si>
   <si>
     <t>99120001187</t>
   </si>
   <si>
+    <t>99120001188</t>
+  </si>
+  <si>
     <t>99120001190</t>
   </si>
   <si>
     <t>99120001191</t>
   </si>
   <si>
-    <t>99120001188</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -980,15 +995,15 @@
     <t>27</t>
   </si>
   <si>
+    <t>99120001213</t>
+  </si>
+  <si>
+    <t>99120001214</t>
+  </si>
+  <si>
     <t>99120001209</t>
   </si>
   <si>
-    <t>99120001213</t>
-  </si>
-  <si>
-    <t>99120001214</t>
-  </si>
-  <si>
     <t>99120001211</t>
   </si>
   <si>
@@ -1013,12 +1028,12 @@
     <t>99120001221</t>
   </si>
   <si>
+    <t>99120001222</t>
+  </si>
+  <si>
     <t>99120001223</t>
   </si>
   <si>
-    <t>99120001222</t>
-  </si>
-  <si>
     <t>99120001217</t>
   </si>
   <si>
@@ -1037,6 +1052,9 @@
     <t>99120001232</t>
   </si>
   <si>
+    <t>99120001225</t>
+  </si>
+  <si>
     <t>99120001226</t>
   </si>
   <si>
@@ -1055,9 +1073,6 @@
     <t>99120001231</t>
   </si>
   <si>
-    <t>99120001225</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -1076,10 +1091,10 @@
     <t>99120001240</t>
   </si>
   <si>
+    <t>99120001236</t>
+  </si>
+  <si>
     <t>99120001234</t>
-  </si>
-  <si>
-    <t>99120001236</t>
   </si>
   <si>
     <t>99120001238</t>
@@ -1321,19 +1336,19 @@
         <v>35</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I5" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>20</v>
@@ -1353,22 +1368,22 @@
         <v>34</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I6" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>20</v>
@@ -1388,10 +1403,10 @@
         <v>34</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>46</v>
@@ -1493,13 +1508,13 @@
         <v>13</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>58</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" s="0" t="s">
         <v>63</v>
@@ -1569,7 +1584,7 @@
         <v>68</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H12" s="0" t="s">
         <v>69</v>
@@ -1604,7 +1619,7 @@
         <v>71</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H13" s="0" t="s">
         <v>72</v>
@@ -1668,7 +1683,7 @@
         <v>34</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>68</v>
@@ -1703,7 +1718,7 @@
         <v>56</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>74</v>
@@ -1773,7 +1788,7 @@
         <v>28</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>86</v>
@@ -1782,7 +1797,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I18" s="0" t="s">
         <v>18</v>
@@ -1849,7 +1864,7 @@
         <v>58</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H20" s="0" t="s">
         <v>60</v>
@@ -1919,7 +1934,7 @@
         <v>86</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>25</v>
@@ -1983,16 +1998,16 @@
         <v>56</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>74</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>18</v>
@@ -2018,7 +2033,7 @@
         <v>56</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>97</v>
@@ -2027,7 +2042,7 @@
         <v>52</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>18</v>
@@ -2053,13 +2068,13 @@
         <v>100</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H26" s="0" t="s">
         <v>79</v>
@@ -2234,7 +2249,7 @@
         <v>58</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>72</v>
@@ -2263,16 +2278,16 @@
         <v>34</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F32" s="0" t="s">
         <v>108</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I32" s="0" t="s">
         <v>18</v>
@@ -2304,7 +2319,7 @@
         <v>86</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H33" s="0" t="s">
         <v>75</v>
@@ -2339,7 +2354,7 @@
         <v>81</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H34" s="0" t="s">
         <v>82</v>
@@ -2368,7 +2383,7 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F35" s="0" t="s">
         <v>113</v>
@@ -2438,16 +2453,16 @@
         <v>28</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I37" s="0" t="s">
         <v>18</v>
@@ -2508,16 +2523,16 @@
         <v>34</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I39" s="0" t="s">
         <v>18</v>
@@ -2543,16 +2558,16 @@
         <v>34</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I40" s="0" t="s">
         <v>18</v>
@@ -2578,7 +2593,7 @@
         <v>49</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F41" s="0" t="s">
         <v>58</v>
@@ -2689,7 +2704,7 @@
         <v>124</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>25</v>
@@ -2718,16 +2733,16 @@
         <v>34</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H45" s="0" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I45" s="0" t="s">
         <v>18</v>
@@ -2753,16 +2768,16 @@
         <v>34</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I46" s="0" t="s">
         <v>18</v>
@@ -2794,7 +2809,7 @@
         <v>15</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H47" s="0" t="s">
         <v>17</v>
@@ -2823,16 +2838,16 @@
         <v>34</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>57</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I48" s="0" t="s">
         <v>18</v>
@@ -2858,7 +2873,7 @@
         <v>49</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>68</v>
@@ -2963,7 +2978,7 @@
         <v>28</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F52" s="0" t="s">
         <v>51</v>
@@ -3033,16 +3048,16 @@
         <v>34</v>
       </c>
       <c r="E54" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F54" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="F54" s="0" t="s">
-        <v>58</v>
-      </c>
       <c r="G54" s="0" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="I54" s="0" t="s">
         <v>18</v>
@@ -3071,13 +3086,13 @@
         <v>46</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H55" s="0" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="I55" s="0" t="s">
         <v>18</v>
@@ -3103,16 +3118,16 @@
         <v>49</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F56" s="0" t="s">
         <v>108</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I56" s="0" t="s">
         <v>18</v>
@@ -3176,10 +3191,10 @@
         <v>14</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H58" s="0" t="s">
         <v>17</v>
@@ -3249,7 +3264,7 @@
         <v>23</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H60" s="0" t="s">
         <v>69</v>
@@ -3278,16 +3293,16 @@
         <v>34</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I61" s="0" t="s">
         <v>18</v>
@@ -3313,16 +3328,16 @@
         <v>34</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F62" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H62" s="0" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I62" s="0" t="s">
         <v>18</v>
@@ -3348,7 +3363,7 @@
         <v>34</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>68</v>
@@ -3357,7 +3372,7 @@
         <v>16</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I63" s="0" t="s">
         <v>18</v>
@@ -3383,7 +3398,7 @@
         <v>21</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F64" s="0" t="s">
         <v>148</v>
@@ -3418,7 +3433,7 @@
         <v>150</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>15</v>
@@ -3427,7 +3442,7 @@
         <v>31</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I65" s="0" t="s">
         <v>18</v>
@@ -3459,7 +3474,7 @@
         <v>15</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H66" s="0" t="s">
         <v>75</v>
@@ -3488,16 +3503,16 @@
         <v>13</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F67" s="0" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H67" s="0" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I67" s="0" t="s">
         <v>18</v>
@@ -3523,16 +3538,16 @@
         <v>13</v>
       </c>
       <c r="E68" s="0" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F68" s="0" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H68" s="0" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="I68" s="0" t="s">
         <v>18</v>
@@ -3558,16 +3573,16 @@
         <v>13</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="I69" s="0" t="s">
         <v>18</v>
@@ -3593,22 +3608,22 @@
         <v>13</v>
       </c>
       <c r="E70" s="0" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="H70" s="0" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="I70" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J70" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K70" s="0" t="s">
         <v>20</v>
@@ -3628,16 +3643,16 @@
         <v>13</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>158</v>
+        <v>15</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I71" s="0" t="s">
         <v>18</v>
@@ -3698,7 +3713,7 @@
         <v>150</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>30</v>
@@ -3707,7 +3722,7 @@
         <v>57</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>18</v>
@@ -3803,13 +3818,13 @@
         <v>28</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F76" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H76" s="0" t="s">
         <v>63</v>
@@ -3844,7 +3859,7 @@
         <v>23</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H77" s="0" t="s">
         <v>17</v>
@@ -3873,7 +3888,7 @@
         <v>34</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F78" s="0" t="s">
         <v>23</v>
@@ -3882,7 +3897,7 @@
         <v>24</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I78" s="0" t="s">
         <v>18</v>
@@ -3949,7 +3964,7 @@
         <v>58</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H80" s="0" t="s">
         <v>53</v>
@@ -3978,7 +3993,7 @@
         <v>49</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F81" s="0" t="s">
         <v>58</v>
@@ -4013,16 +4028,16 @@
         <v>56</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="I82" s="0" t="s">
         <v>18</v>
@@ -4048,16 +4063,16 @@
         <v>56</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>18</v>
@@ -4089,7 +4104,7 @@
         <v>15</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H84" s="0" t="s">
         <v>72</v>
@@ -4118,16 +4133,16 @@
         <v>56</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="I85" s="0" t="s">
         <v>18</v>
@@ -4153,16 +4168,16 @@
         <v>56</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F86" s="0" t="s">
         <v>108</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="I86" s="0" t="s">
         <v>18</v>
@@ -4188,16 +4203,16 @@
         <v>56</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I87" s="0" t="s">
         <v>18</v>
@@ -4229,7 +4244,7 @@
         <v>15</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H88" s="0" t="s">
         <v>25</v>
@@ -4258,7 +4273,7 @@
         <v>56</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F89" s="0" t="s">
         <v>74</v>
@@ -4293,16 +4308,16 @@
         <v>34</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F90" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="I90" s="0" t="s">
         <v>18</v>
@@ -4328,16 +4343,16 @@
         <v>34</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F91" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="I91" s="0" t="s">
         <v>18</v>
@@ -4398,16 +4413,16 @@
         <v>34</v>
       </c>
       <c r="E93" s="0" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F93" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H93" s="0" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="I93" s="0" t="s">
         <v>18</v>
@@ -4439,7 +4454,7 @@
         <v>181</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H94" s="0" t="s">
         <v>82</v>
@@ -4544,7 +4559,7 @@
         <v>181</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H97" s="0" t="s">
         <v>60</v>
@@ -4579,7 +4594,7 @@
         <v>68</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H98" s="0" t="s">
         <v>72</v>
@@ -4608,7 +4623,7 @@
         <v>13</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F99" s="0" t="s">
         <v>108</v>
@@ -4617,7 +4632,7 @@
         <v>22</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I99" s="0" t="s">
         <v>18</v>
@@ -4649,7 +4664,7 @@
         <v>51</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H100" s="0" t="s">
         <v>53</v>
@@ -4678,7 +4693,7 @@
         <v>28</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F101" s="0" t="s">
         <v>68</v>
@@ -4687,7 +4702,7 @@
         <v>59</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I101" s="0" t="s">
         <v>18</v>
@@ -4719,7 +4734,7 @@
         <v>15</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H102" s="0" t="s">
         <v>75</v>
@@ -4748,7 +4763,7 @@
         <v>34</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F103" s="0" t="s">
         <v>108</v>
@@ -4821,7 +4836,7 @@
         <v>57</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>16</v>
@@ -4853,16 +4868,16 @@
         <v>56</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F106" s="0" t="s">
         <v>201</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I106" s="0" t="s">
         <v>18</v>
@@ -4891,7 +4906,7 @@
         <v>59</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>52</v>
@@ -4958,16 +4973,16 @@
         <v>13</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="I109" s="0" t="s">
         <v>18</v>
@@ -4993,16 +5008,16 @@
         <v>13</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I110" s="0" t="s">
         <v>18</v>
@@ -5104,7 +5119,7 @@
         <v>15</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H113" s="0" t="s">
         <v>66</v>
@@ -5139,7 +5154,7 @@
         <v>113</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H114" s="0" t="s">
         <v>53</v>
@@ -5174,7 +5189,7 @@
         <v>74</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H115" s="0" t="s">
         <v>32</v>
@@ -5209,7 +5224,7 @@
         <v>97</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H116" s="0" t="s">
         <v>75</v>
@@ -5238,16 +5253,16 @@
         <v>34</v>
       </c>
       <c r="E117" s="0" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="F117" s="0" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="G117" s="0" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="H117" s="0" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>18</v>
@@ -5273,22 +5288,22 @@
         <v>34</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="F118" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="G118" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="H118" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="I118" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J118" s="0" t="s">
         <v>215</v>
-      </c>
-      <c r="G118" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="H118" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="I118" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="J118" s="0" t="s">
-        <v>216</v>
       </c>
       <c r="K118" s="0" t="s">
         <v>20</v>
@@ -5308,16 +5323,16 @@
         <v>34</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>88</v>
+        <v>216</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>18</v>
@@ -5343,7 +5358,7 @@
         <v>49</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F120" s="0" t="s">
         <v>58</v>
@@ -5352,7 +5367,7 @@
         <v>16</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I120" s="0" t="s">
         <v>18</v>
@@ -5381,7 +5396,7 @@
         <v>24</v>
       </c>
       <c r="F121" s="0" t="s">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="G121" s="0" t="s">
         <v>52</v>
@@ -5413,16 +5428,16 @@
         <v>56</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F122" s="0" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="G122" s="0" t="s">
         <v>14</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I122" s="0" t="s">
         <v>18</v>
@@ -5451,10 +5466,10 @@
         <v>59</v>
       </c>
       <c r="F123" s="0" t="s">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H123" s="0" t="s">
         <v>82</v>
@@ -5486,10 +5501,10 @@
         <v>52</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H124" s="0" t="s">
         <v>72</v>
@@ -5518,10 +5533,10 @@
         <v>21</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F125" s="0" t="s">
-        <v>181</v>
+        <v>88</v>
       </c>
       <c r="G125" s="0" t="s">
         <v>16</v>
@@ -5553,22 +5568,22 @@
         <v>34</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="F126" s="0" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="G126" s="0" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="H126" s="0" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I126" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J126" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K126" s="0" t="s">
         <v>20</v>
@@ -5588,22 +5603,22 @@
         <v>34</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J127" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K127" s="0" t="s">
         <v>20</v>
@@ -5623,22 +5638,22 @@
         <v>34</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F128" s="0" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="G128" s="0" t="s">
         <v>50</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I128" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J128" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K128" s="0" t="s">
         <v>20</v>
@@ -5661,7 +5676,7 @@
         <v>31</v>
       </c>
       <c r="F129" s="0" t="s">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="G129" s="0" t="s">
         <v>24</v>
@@ -5673,7 +5688,7 @@
         <v>18</v>
       </c>
       <c r="J129" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K129" s="0" t="s">
         <v>20</v>
@@ -5681,7 +5696,7 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B130" s="2">
         <v>46141.791666666664</v>
@@ -5696,7 +5711,7 @@
         <v>50</v>
       </c>
       <c r="F130" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G130" s="0" t="s">
         <v>31</v>
@@ -5708,7 +5723,7 @@
         <v>18</v>
       </c>
       <c r="J130" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K130" s="0" t="s">
         <v>20</v>
@@ -5716,7 +5731,7 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B131" s="2">
         <v>46241.791666666664</v>
@@ -5728,13 +5743,13 @@
         <v>56</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F131" s="0" t="s">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H131" s="0" t="s">
         <v>77</v>
@@ -5743,7 +5758,7 @@
         <v>18</v>
       </c>
       <c r="J131" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K131" s="0" t="s">
         <v>20</v>
@@ -5751,7 +5766,7 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B132" s="2">
         <v>46242.583333333336</v>
@@ -5763,22 +5778,22 @@
         <v>100</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>59</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I132" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J132" s="0" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K132" s="0" t="s">
         <v>20</v>
@@ -5786,7 +5801,7 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B133" s="2">
         <v>46242.666666666664</v>
@@ -5801,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="F133" s="0" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="G133" s="0" t="s">
         <v>57</v>
@@ -5813,7 +5828,7 @@
         <v>18</v>
       </c>
       <c r="J133" s="0" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K133" s="0" t="s">
         <v>20</v>
@@ -5821,7 +5836,7 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B134" s="2">
         <v>46242.75</v>
@@ -5833,10 +5848,10 @@
         <v>21</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F134" s="0" t="s">
-        <v>181</v>
+        <v>86</v>
       </c>
       <c r="G134" s="0" t="s">
         <v>52</v>
@@ -5848,7 +5863,7 @@
         <v>18</v>
       </c>
       <c r="J134" s="0" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K134" s="0" t="s">
         <v>20</v>
@@ -5856,7 +5871,7 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B135" s="2">
         <v>46243.604166666664</v>
@@ -5868,10 +5883,10 @@
         <v>28</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F135" s="0" t="s">
-        <v>181</v>
+        <v>68</v>
       </c>
       <c r="G135" s="0" t="s">
         <v>24</v>
@@ -5883,7 +5898,7 @@
         <v>18</v>
       </c>
       <c r="J135" s="0" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K135" s="0" t="s">
         <v>20</v>
@@ -5891,7 +5906,7 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B136" s="2">
         <v>46243.708333333336</v>
@@ -5906,10 +5921,10 @@
         <v>14</v>
       </c>
       <c r="F136" s="0" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H136" s="0" t="s">
         <v>17</v>
@@ -5918,7 +5933,7 @@
         <v>18</v>
       </c>
       <c r="J136" s="0" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K136" s="0" t="s">
         <v>20</v>
@@ -5926,7 +5941,7 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B137" s="2">
         <v>46243.802083333336</v>
@@ -5941,7 +5956,7 @@
         <v>29</v>
       </c>
       <c r="F137" s="0" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="G137" s="0" t="s">
         <v>22</v>
@@ -5953,7 +5968,7 @@
         <v>18</v>
       </c>
       <c r="J137" s="0" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K137" s="0" t="s">
         <v>20</v>
@@ -5961,7 +5976,7 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B138" s="2">
         <v>46142.791666666664</v>
@@ -5979,7 +5994,7 @@
         <v>103</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H138" s="0" t="s">
         <v>82</v>
@@ -5988,7 +6003,7 @@
         <v>18</v>
       </c>
       <c r="J138" s="0" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K138" s="0" t="s">
         <v>20</v>
@@ -5996,7 +6011,7 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B139" s="2">
         <v>46248.791666666664</v>
@@ -6011,7 +6026,7 @@
         <v>24</v>
       </c>
       <c r="F139" s="0" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="G139" s="0" t="s">
         <v>16</v>
@@ -6023,7 +6038,7 @@
         <v>18</v>
       </c>
       <c r="J139" s="0" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K139" s="0" t="s">
         <v>20</v>
@@ -6031,7 +6046,7 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B140" s="2">
         <v>46249.666666666664</v>
@@ -6043,22 +6058,22 @@
         <v>13</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I140" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J140" s="0" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K140" s="0" t="s">
         <v>20</v>
@@ -6066,7 +6081,7 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B141" s="2">
         <v>46250.604166666664</v>
@@ -6078,22 +6093,22 @@
         <v>28</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F141" s="0" t="s">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I141" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J141" s="0" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K141" s="0" t="s">
         <v>20</v>
@@ -6101,7 +6116,7 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B142" s="2">
         <v>46250.708333333336</v>
@@ -6116,7 +6131,7 @@
         <v>22</v>
       </c>
       <c r="F142" s="0" t="s">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="G142" s="0" t="s">
         <v>50</v>
@@ -6128,7 +6143,7 @@
         <v>18</v>
       </c>
       <c r="J142" s="0" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K142" s="0" t="s">
         <v>20</v>
@@ -6136,7 +6151,7 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B143" s="2">
         <v>46250.708333333336</v>
@@ -6151,10 +6166,10 @@
         <v>57</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H143" s="0" t="s">
         <v>60</v>
@@ -6163,7 +6178,7 @@
         <v>18</v>
       </c>
       <c r="J143" s="0" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K143" s="0" t="s">
         <v>20</v>
@@ -6171,7 +6186,7 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B144" s="2">
         <v>46250.708333333336</v>
@@ -6186,7 +6201,7 @@
         <v>31</v>
       </c>
       <c r="F144" s="0" t="s">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="G144" s="0" t="s">
         <v>14</v>
@@ -6198,7 +6213,7 @@
         <v>18</v>
       </c>
       <c r="J144" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K144" s="0" t="s">
         <v>20</v>
@@ -6206,7 +6221,7 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B145" s="2">
         <v>46250.802083333336</v>
@@ -6221,7 +6236,7 @@
         <v>52</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>29</v>
@@ -6233,7 +6248,7 @@
         <v>18</v>
       </c>
       <c r="J145" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K145" s="0" t="s">
         <v>20</v>
@@ -6241,34 +6256,34 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B146" s="2">
-        <v>46263.666666666664</v>
+        <v>46264.604166666664</v>
       </c>
       <c r="C146" s="0" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E146" s="0" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F146" s="0" t="s">
-        <v>181</v>
+        <v>253</v>
       </c>
       <c r="G146" s="0" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H146" s="0" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J146" s="0" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K146" s="0" t="s">
         <v>20</v>
@@ -6276,34 +6291,34 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B147" s="2">
-        <v>46263.75</v>
+        <v>46264.708333333336</v>
       </c>
       <c r="C147" s="0" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E147" s="0" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="G147" s="0" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="H147" s="0" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="I147" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J147" s="0" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="K147" s="0" t="s">
         <v>20</v>
@@ -6311,34 +6326,34 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B148" s="2">
-        <v>46264.604166666664</v>
+        <v>46264.708333333336</v>
       </c>
       <c r="C148" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J148" s="0" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K148" s="0" t="s">
         <v>20</v>
@@ -6346,7 +6361,7 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B149" s="2">
         <v>46264.708333333336</v>
@@ -6358,22 +6373,22 @@
         <v>34</v>
       </c>
       <c r="E149" s="0" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F149" s="0" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
       <c r="G149" s="0" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="H149" s="0" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="I149" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J149" s="0" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K149" s="0" t="s">
         <v>20</v>
@@ -6381,7 +6396,7 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B150" s="2">
         <v>46264.708333333336</v>
@@ -6393,13 +6408,13 @@
         <v>34</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>181</v>
+        <v>65</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H150" s="0" t="s">
         <v>63</v>
@@ -6408,7 +6423,7 @@
         <v>18</v>
       </c>
       <c r="J150" s="0" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K150" s="0" t="s">
         <v>20</v>
@@ -6416,7 +6431,7 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B151" s="2">
         <v>46264.708333333336</v>
@@ -6428,22 +6443,22 @@
         <v>34</v>
       </c>
       <c r="E151" s="0" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F151" s="0" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="H151" s="0" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I151" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J151" s="0" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K151" s="0" t="s">
         <v>20</v>
@@ -6451,7 +6466,7 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B152" s="2">
         <v>46264.708333333336</v>
@@ -6463,22 +6478,22 @@
         <v>34</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F152" s="0" t="s">
-        <v>181</v>
+        <v>260</v>
       </c>
       <c r="G152" s="0" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J152" s="0" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K152" s="0" t="s">
         <v>20</v>
@@ -6486,7 +6501,7 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B153" s="2">
         <v>46264.802083333336</v>
@@ -6498,10 +6513,10 @@
         <v>49</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F153" s="0" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="G153" s="0" t="s">
         <v>52</v>
@@ -6513,7 +6528,7 @@
         <v>18</v>
       </c>
       <c r="J153" s="0" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K153" s="0" t="s">
         <v>20</v>
@@ -6521,7 +6536,7 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B154" s="2">
         <v>46269.791666666664</v>
@@ -6533,22 +6548,22 @@
         <v>56</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F154" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="I154" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J154" s="0" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K154" s="0" t="s">
         <v>20</v>
@@ -6556,7 +6571,7 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B155" s="2">
         <v>46269.791666666664</v>
@@ -6568,22 +6583,22 @@
         <v>56</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F155" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="I155" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J155" s="0" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K155" s="0" t="s">
         <v>20</v>
@@ -6591,7 +6606,7 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B156" s="2">
         <v>46269.875</v>
@@ -6603,7 +6618,7 @@
         <v>222</v>
       </c>
       <c r="E156" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F156" s="0" t="s">
         <v>181</v>
@@ -6618,7 +6633,7 @@
         <v>18</v>
       </c>
       <c r="J156" s="0" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K156" s="0" t="s">
         <v>20</v>
@@ -6626,7 +6641,7 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B157" s="2">
         <v>46270.666666666664</v>
@@ -6653,7 +6668,7 @@
         <v>18</v>
       </c>
       <c r="J157" s="0" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K157" s="0" t="s">
         <v>20</v>
@@ -6661,7 +6676,7 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B158" s="2">
         <v>46270.75</v>
@@ -6679,7 +6694,7 @@
         <v>181</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H158" s="0" t="s">
         <v>75</v>
@@ -6688,7 +6703,7 @@
         <v>18</v>
       </c>
       <c r="J158" s="0" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K158" s="0" t="s">
         <v>20</v>
@@ -6696,7 +6711,7 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B159" s="2">
         <v>46271.708333333336</v>
@@ -6708,7 +6723,7 @@
         <v>34</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="F159" s="0" t="s">
         <v>181</v>
@@ -6717,13 +6732,13 @@
         <v>35</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J159" s="0" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K159" s="0" t="s">
         <v>20</v>
@@ -6731,34 +6746,34 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B160" s="2">
-        <v>46271.802083333336</v>
+        <v>46271.708333333336</v>
       </c>
       <c r="C160" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F160" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G160" s="0" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I160" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J160" s="0" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K160" s="0" t="s">
         <v>20</v>
@@ -6766,34 +6781,34 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B161" s="2">
-        <v>46272.791666666664</v>
+        <v>46271.802083333336</v>
       </c>
       <c r="C161" s="0" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E161" s="0" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="F161" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G161" s="0" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H161" s="0" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="I161" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J161" s="0" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K161" s="0" t="s">
         <v>20</v>
@@ -6801,7 +6816,7 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B162" s="2">
         <v>46277.666666666664</v>
@@ -6813,13 +6828,13 @@
         <v>13</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F162" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H162" s="0" t="s">
         <v>79</v>
@@ -6828,7 +6843,7 @@
         <v>18</v>
       </c>
       <c r="J162" s="0" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K162" s="0" t="s">
         <v>20</v>
@@ -6836,7 +6851,7 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B163" s="2">
         <v>46277.75</v>
@@ -6863,7 +6878,7 @@
         <v>18</v>
       </c>
       <c r="J163" s="0" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K163" s="0" t="s">
         <v>20</v>
@@ -6871,7 +6886,7 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B164" s="2">
         <v>46278.604166666664</v>
@@ -6898,7 +6913,7 @@
         <v>18</v>
       </c>
       <c r="J164" s="0" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K164" s="0" t="s">
         <v>20</v>
@@ -6906,7 +6921,7 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B165" s="2">
         <v>46278.708333333336</v>
@@ -6918,22 +6933,22 @@
         <v>34</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F165" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I165" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J165" s="0" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K165" s="0" t="s">
         <v>20</v>
@@ -6941,7 +6956,7 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B166" s="2">
         <v>46278.708333333336</v>
@@ -6953,7 +6968,7 @@
         <v>34</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F166" s="0" t="s">
         <v>181</v>
@@ -6968,7 +6983,7 @@
         <v>18</v>
       </c>
       <c r="J166" s="0" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K166" s="0" t="s">
         <v>20</v>
@@ -6976,7 +6991,7 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B167" s="2">
         <v>46278.708333333336</v>
@@ -6988,22 +7003,22 @@
         <v>34</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F167" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="I167" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J167" s="0" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K167" s="0" t="s">
         <v>20</v>
@@ -7011,7 +7026,7 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B168" s="2">
         <v>46278.708333333336</v>
@@ -7023,22 +7038,22 @@
         <v>34</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F168" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I168" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J168" s="0" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K168" s="0" t="s">
         <v>20</v>
@@ -7046,7 +7061,7 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B169" s="2">
         <v>46278.802083333336</v>
@@ -7073,7 +7088,7 @@
         <v>18</v>
       </c>
       <c r="J169" s="0" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K169" s="0" t="s">
         <v>20</v>
@@ -7081,7 +7096,7 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B170" s="2">
         <v>46283.791666666664</v>
@@ -7099,7 +7114,7 @@
         <v>181</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H170" s="0" t="s">
         <v>60</v>
@@ -7108,7 +7123,7 @@
         <v>18</v>
       </c>
       <c r="J170" s="0" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K170" s="0" t="s">
         <v>20</v>
@@ -7116,7 +7131,7 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B171" s="2">
         <v>46284.666666666664</v>
@@ -7143,7 +7158,7 @@
         <v>18</v>
       </c>
       <c r="J171" s="0" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K171" s="0" t="s">
         <v>20</v>
@@ -7151,7 +7166,7 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B172" s="2">
         <v>46284.75</v>
@@ -7169,7 +7184,7 @@
         <v>181</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H172" s="0" t="s">
         <v>25</v>
@@ -7178,7 +7193,7 @@
         <v>18</v>
       </c>
       <c r="J172" s="0" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K172" s="0" t="s">
         <v>20</v>
@@ -7186,7 +7201,7 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B173" s="2">
         <v>46285.604166666664</v>
@@ -7198,7 +7213,7 @@
         <v>28</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F173" s="0" t="s">
         <v>181</v>
@@ -7207,13 +7222,13 @@
         <v>52</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I173" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J173" s="0" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K173" s="0" t="s">
         <v>20</v>
@@ -7221,7 +7236,7 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B174" s="2">
         <v>46285.708333333336</v>
@@ -7233,22 +7248,22 @@
         <v>34</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F174" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I174" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J174" s="0" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K174" s="0" t="s">
         <v>20</v>
@@ -7256,7 +7271,7 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B175" s="2">
         <v>46285.708333333336</v>
@@ -7268,22 +7283,22 @@
         <v>34</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F175" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I175" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J175" s="0" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K175" s="0" t="s">
         <v>20</v>
@@ -7291,7 +7306,7 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B176" s="2">
         <v>46285.708333333336</v>
@@ -7303,22 +7318,22 @@
         <v>34</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F176" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="I176" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J176" s="0" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K176" s="0" t="s">
         <v>20</v>
@@ -7326,7 +7341,7 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B177" s="2">
         <v>46285.802083333336</v>
@@ -7353,7 +7368,7 @@
         <v>18</v>
       </c>
       <c r="J177" s="0" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K177" s="0" t="s">
         <v>20</v>
@@ -7361,7 +7376,7 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B178" s="2">
         <v>46306.708333333336</v>
@@ -7373,22 +7388,22 @@
         <v>34</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F178" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J178" s="0" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K178" s="0" t="s">
         <v>20</v>
@@ -7396,7 +7411,7 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B179" s="2">
         <v>46306.708333333336</v>
@@ -7408,7 +7423,7 @@
         <v>34</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F179" s="0" t="s">
         <v>181</v>
@@ -7423,7 +7438,7 @@
         <v>18</v>
       </c>
       <c r="J179" s="0" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K179" s="0" t="s">
         <v>20</v>
@@ -7431,7 +7446,7 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B180" s="2">
         <v>46306.708333333336</v>
@@ -7458,7 +7473,7 @@
         <v>18</v>
       </c>
       <c r="J180" s="0" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K180" s="0" t="s">
         <v>20</v>
@@ -7466,7 +7481,7 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B181" s="2">
         <v>46306.708333333336</v>
@@ -7493,7 +7508,7 @@
         <v>18</v>
       </c>
       <c r="J181" s="0" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K181" s="0" t="s">
         <v>20</v>
@@ -7501,7 +7516,7 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B182" s="2">
         <v>46306.708333333336</v>
@@ -7528,7 +7543,7 @@
         <v>18</v>
       </c>
       <c r="J182" s="0" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K182" s="0" t="s">
         <v>20</v>
@@ -7536,7 +7551,7 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B183" s="2">
         <v>46306.708333333336</v>
@@ -7548,22 +7563,22 @@
         <v>34</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I183" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J183" s="0" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K183" s="0" t="s">
         <v>20</v>
@@ -7571,7 +7586,7 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B184" s="2">
         <v>46306.708333333336</v>
@@ -7583,22 +7598,22 @@
         <v>34</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F184" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="I184" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J184" s="0" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K184" s="0" t="s">
         <v>20</v>
@@ -7606,7 +7621,7 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B185" s="2">
         <v>46306.708333333336</v>
@@ -7618,22 +7633,22 @@
         <v>34</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="I185" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J185" s="0" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="K185" s="0" t="s">
         <v>20</v>
@@ -7641,7 +7656,7 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B186" s="2">
         <v>46313.708333333336</v>
@@ -7659,7 +7674,7 @@
         <v>181</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H186" s="0" t="s">
         <v>32</v>
@@ -7668,7 +7683,7 @@
         <v>18</v>
       </c>
       <c r="J186" s="0" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K186" s="0" t="s">
         <v>20</v>
@@ -7676,7 +7691,7 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B187" s="2">
         <v>46313.708333333336</v>
@@ -7688,22 +7703,22 @@
         <v>34</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="F187" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="I187" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J187" s="0" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K187" s="0" t="s">
         <v>20</v>
@@ -7711,7 +7726,7 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B188" s="2">
         <v>46313.708333333336</v>
@@ -7723,22 +7738,22 @@
         <v>34</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F188" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G188" s="0" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I188" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J188" s="0" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K188" s="0" t="s">
         <v>20</v>
@@ -7746,7 +7761,7 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B189" s="2">
         <v>46313.708333333336</v>
@@ -7773,7 +7788,7 @@
         <v>18</v>
       </c>
       <c r="J189" s="0" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="K189" s="0" t="s">
         <v>20</v>
@@ -7781,7 +7796,7 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B190" s="2">
         <v>46313.708333333336</v>
@@ -7799,7 +7814,7 @@
         <v>181</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H190" s="0" t="s">
         <v>25</v>
@@ -7808,7 +7823,7 @@
         <v>18</v>
       </c>
       <c r="J190" s="0" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K190" s="0" t="s">
         <v>20</v>
@@ -7816,7 +7831,7 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B191" s="2">
         <v>46313.708333333336</v>
@@ -7828,22 +7843,22 @@
         <v>34</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I191" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J191" s="0" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K191" s="0" t="s">
         <v>20</v>
@@ -7851,7 +7866,7 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B192" s="2">
         <v>46313.708333333336</v>
@@ -7863,22 +7878,22 @@
         <v>34</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F192" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J192" s="0" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K192" s="0" t="s">
         <v>20</v>
@@ -7886,7 +7901,7 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B193" s="2">
         <v>46313.708333333336</v>
@@ -7898,22 +7913,22 @@
         <v>34</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F193" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G193" s="0" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="I193" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J193" s="0" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K193" s="0" t="s">
         <v>20</v>
@@ -7921,7 +7936,7 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B194" s="2">
         <v>46327.708333333336</v>
@@ -7948,7 +7963,7 @@
         <v>18</v>
       </c>
       <c r="J194" s="0" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K194" s="0" t="s">
         <v>20</v>
@@ -7956,7 +7971,7 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B195" s="2">
         <v>46327.708333333336</v>
@@ -7968,7 +7983,7 @@
         <v>34</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>181</v>
@@ -7977,13 +7992,13 @@
         <v>50</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J195" s="0" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K195" s="0" t="s">
         <v>20</v>
@@ -7991,7 +8006,7 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B196" s="2">
         <v>46327.708333333336</v>
@@ -8018,7 +8033,7 @@
         <v>18</v>
       </c>
       <c r="J196" s="0" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K196" s="0" t="s">
         <v>20</v>
@@ -8026,7 +8041,7 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B197" s="2">
         <v>46327.708333333336</v>
@@ -8053,7 +8068,7 @@
         <v>18</v>
       </c>
       <c r="J197" s="0" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K197" s="0" t="s">
         <v>20</v>
@@ -8061,7 +8076,7 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B198" s="2">
         <v>46327.708333333336</v>
@@ -8088,7 +8103,7 @@
         <v>18</v>
       </c>
       <c r="J198" s="0" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K198" s="0" t="s">
         <v>20</v>
@@ -8096,7 +8111,7 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B199" s="2">
         <v>46327.708333333336</v>
@@ -8108,7 +8123,7 @@
         <v>34</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F199" s="0" t="s">
         <v>181</v>
@@ -8117,13 +8132,13 @@
         <v>14</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I199" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J199" s="0" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K199" s="0" t="s">
         <v>20</v>
@@ -8131,7 +8146,7 @@
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B200" s="2">
         <v>46327.708333333336</v>
@@ -8143,13 +8158,13 @@
         <v>34</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F200" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H200" s="0" t="s">
         <v>63</v>
@@ -8158,7 +8173,7 @@
         <v>18</v>
       </c>
       <c r="J200" s="0" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K200" s="0" t="s">
         <v>20</v>
@@ -8166,7 +8181,7 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B201" s="2">
         <v>46327.708333333336</v>
@@ -8178,22 +8193,22 @@
         <v>34</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F201" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I201" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J201" s="0" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K201" s="0" t="s">
         <v>20</v>
@@ -8201,7 +8216,7 @@
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B202" s="2">
         <v>46334.708333333336</v>
@@ -8219,7 +8234,7 @@
         <v>181</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H202" s="0" t="s">
         <v>69</v>
@@ -8228,7 +8243,7 @@
         <v>18</v>
       </c>
       <c r="J202" s="0" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K202" s="0" t="s">
         <v>20</v>
@@ -8236,7 +8251,7 @@
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B203" s="2">
         <v>46334.708333333336</v>
@@ -8254,7 +8269,7 @@
         <v>181</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H203" s="0" t="s">
         <v>66</v>
@@ -8263,7 +8278,7 @@
         <v>18</v>
       </c>
       <c r="J203" s="0" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K203" s="0" t="s">
         <v>20</v>
@@ -8271,7 +8286,7 @@
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B204" s="2">
         <v>46334.708333333336</v>
@@ -8283,7 +8298,7 @@
         <v>34</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F204" s="0" t="s">
         <v>181</v>
@@ -8298,7 +8313,7 @@
         <v>18</v>
       </c>
       <c r="J204" s="0" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K204" s="0" t="s">
         <v>20</v>
@@ -8306,7 +8321,7 @@
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B205" s="2">
         <v>46334.708333333336</v>
@@ -8333,7 +8348,7 @@
         <v>18</v>
       </c>
       <c r="J205" s="0" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K205" s="0" t="s">
         <v>20</v>
@@ -8341,7 +8356,7 @@
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B206" s="2">
         <v>46334.708333333336</v>
@@ -8368,7 +8383,7 @@
         <v>18</v>
       </c>
       <c r="J206" s="0" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="K206" s="0" t="s">
         <v>20</v>
@@ -8376,7 +8391,7 @@
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B207" s="2">
         <v>46334.708333333336</v>
@@ -8394,7 +8409,7 @@
         <v>181</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H207" s="0" t="s">
         <v>32</v>
@@ -8403,7 +8418,7 @@
         <v>18</v>
       </c>
       <c r="J207" s="0" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K207" s="0" t="s">
         <v>20</v>
@@ -8411,7 +8426,7 @@
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B208" s="2">
         <v>46334.708333333336</v>
@@ -8423,13 +8438,13 @@
         <v>34</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F208" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H208" s="0" t="s">
         <v>79</v>
@@ -8438,7 +8453,7 @@
         <v>18</v>
       </c>
       <c r="J208" s="0" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K208" s="0" t="s">
         <v>20</v>
@@ -8446,7 +8461,7 @@
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B209" s="2">
         <v>46334.708333333336</v>
@@ -8473,7 +8488,7 @@
         <v>18</v>
       </c>
       <c r="J209" s="0" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K209" s="0" t="s">
         <v>20</v>
@@ -8481,7 +8496,7 @@
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B210" s="2">
         <v>46348.708333333336</v>
@@ -8493,22 +8508,22 @@
         <v>34</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="F210" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I210" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J210" s="0" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K210" s="0" t="s">
         <v>20</v>
@@ -8516,7 +8531,7 @@
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B211" s="2">
         <v>46348.708333333336</v>
@@ -8528,22 +8543,22 @@
         <v>34</v>
       </c>
       <c r="E211" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F211" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H211" s="0" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I211" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J211" s="0" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K211" s="0" t="s">
         <v>20</v>
@@ -8551,7 +8566,7 @@
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B212" s="2">
         <v>46348.708333333336</v>
@@ -8563,22 +8578,22 @@
         <v>34</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="F212" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I212" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J212" s="0" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K212" s="0" t="s">
         <v>20</v>
@@ -8586,7 +8601,7 @@
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B213" s="2">
         <v>46348.708333333336</v>
@@ -8604,7 +8619,7 @@
         <v>181</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H213" s="0" t="s">
         <v>32</v>
@@ -8613,7 +8628,7 @@
         <v>18</v>
       </c>
       <c r="J213" s="0" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="K213" s="0" t="s">
         <v>20</v>
@@ -8621,7 +8636,7 @@
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B214" s="2">
         <v>46348.708333333336</v>
@@ -8633,7 +8648,7 @@
         <v>34</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F214" s="0" t="s">
         <v>181</v>
@@ -8642,13 +8657,13 @@
         <v>31</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I214" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J214" s="0" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K214" s="0" t="s">
         <v>20</v>
@@ -8656,7 +8671,7 @@
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B215" s="2">
         <v>46348.708333333336</v>
@@ -8683,7 +8698,7 @@
         <v>18</v>
       </c>
       <c r="J215" s="0" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="K215" s="0" t="s">
         <v>20</v>
@@ -8691,7 +8706,7 @@
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B216" s="2">
         <v>46348.708333333336</v>
@@ -8703,22 +8718,22 @@
         <v>34</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F216" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I216" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J216" s="0" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="K216" s="0" t="s">
         <v>20</v>
@@ -8726,7 +8741,7 @@
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B217" s="2">
         <v>46348.708333333336</v>
@@ -8738,7 +8753,7 @@
         <v>34</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F217" s="0" t="s">
         <v>181</v>
@@ -8747,13 +8762,13 @@
         <v>24</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I217" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J217" s="0" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K217" s="0" t="s">
         <v>20</v>
@@ -8761,7 +8776,7 @@
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B218" s="2">
         <v>46355.708333333336</v>
@@ -8788,7 +8803,7 @@
         <v>18</v>
       </c>
       <c r="J218" s="0" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="K218" s="0" t="s">
         <v>20</v>
@@ -8796,7 +8811,7 @@
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B219" s="2">
         <v>46355.708333333336</v>
@@ -8823,7 +8838,7 @@
         <v>18</v>
       </c>
       <c r="J219" s="0" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="K219" s="0" t="s">
         <v>20</v>
@@ -8831,7 +8846,7 @@
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B220" s="2">
         <v>46355.708333333336</v>
@@ -8843,22 +8858,22 @@
         <v>34</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F220" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J220" s="0" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="K220" s="0" t="s">
         <v>20</v>
@@ -8866,7 +8881,7 @@
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B221" s="2">
         <v>46355.708333333336</v>
@@ -8884,16 +8899,16 @@
         <v>181</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="I221" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J221" s="0" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K221" s="0" t="s">
         <v>20</v>
@@ -8901,7 +8916,7 @@
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B222" s="2">
         <v>46355.708333333336</v>
@@ -8919,7 +8934,7 @@
         <v>181</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H222" s="0" t="s">
         <v>82</v>
@@ -8928,7 +8943,7 @@
         <v>18</v>
       </c>
       <c r="J222" s="0" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K222" s="0" t="s">
         <v>20</v>
@@ -8936,7 +8951,7 @@
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B223" s="2">
         <v>46355.708333333336</v>
@@ -8954,7 +8969,7 @@
         <v>181</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H223" s="0" t="s">
         <v>72</v>
@@ -8963,7 +8978,7 @@
         <v>18</v>
       </c>
       <c r="J223" s="0" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="K223" s="0" t="s">
         <v>20</v>
@@ -8971,7 +8986,7 @@
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B224" s="2">
         <v>46355.708333333336</v>
@@ -8983,7 +8998,7 @@
         <v>34</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F224" s="0" t="s">
         <v>181</v>
@@ -8998,7 +9013,7 @@
         <v>18</v>
       </c>
       <c r="J224" s="0" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="K224" s="0" t="s">
         <v>20</v>
@@ -9006,7 +9021,7 @@
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B225" s="2">
         <v>46355.708333333336</v>
@@ -9024,7 +9039,7 @@
         <v>181</v>
       </c>
       <c r="G225" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H225" s="0" t="s">
         <v>66</v>
@@ -9033,7 +9048,7 @@
         <v>18</v>
       </c>
       <c r="J225" s="0" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="K225" s="0" t="s">
         <v>20</v>
@@ -9041,7 +9056,7 @@
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B226" s="2">
         <v>46362.708333333336</v>
@@ -9053,7 +9068,7 @@
         <v>34</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F226" s="0" t="s">
         <v>181</v>
@@ -9062,13 +9077,13 @@
         <v>59</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I226" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J226" s="0" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="K226" s="0" t="s">
         <v>20</v>
@@ -9076,7 +9091,7 @@
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B227" s="2">
         <v>46362.708333333336</v>
@@ -9088,22 +9103,22 @@
         <v>34</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F227" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I227" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J227" s="0" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K227" s="0" t="s">
         <v>20</v>
@@ -9111,7 +9126,7 @@
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B228" s="2">
         <v>46362.708333333336</v>
@@ -9123,22 +9138,22 @@
         <v>34</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F228" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I228" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J228" s="0" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="K228" s="0" t="s">
         <v>20</v>
@@ -9146,7 +9161,7 @@
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B229" s="2">
         <v>46362.708333333336</v>
@@ -9158,22 +9173,22 @@
         <v>34</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F229" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I229" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J229" s="0" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="K229" s="0" t="s">
         <v>20</v>
@@ -9181,7 +9196,7 @@
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B230" s="2">
         <v>46362.708333333336</v>
@@ -9193,22 +9208,22 @@
         <v>34</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I230" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J230" s="0" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K230" s="0" t="s">
         <v>20</v>
@@ -9216,7 +9231,7 @@
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B231" s="2">
         <v>46362.708333333336</v>
@@ -9228,22 +9243,22 @@
         <v>34</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F231" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="I231" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J231" s="0" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="K231" s="0" t="s">
         <v>20</v>
@@ -9251,7 +9266,7 @@
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B232" s="2">
         <v>46362.708333333336</v>
@@ -9263,22 +9278,22 @@
         <v>34</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F232" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="I232" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J232" s="0" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="K232" s="0" t="s">
         <v>20</v>
@@ -9286,7 +9301,7 @@
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B233" s="2">
         <v>46362.708333333336</v>
@@ -9298,22 +9313,22 @@
         <v>34</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F233" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="I233" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J233" s="0" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K233" s="0" t="s">
         <v>20</v>
@@ -9321,7 +9336,7 @@
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B234" s="2">
         <v>46369.708333333336</v>
@@ -9348,7 +9363,7 @@
         <v>18</v>
       </c>
       <c r="J234" s="0" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K234" s="0" t="s">
         <v>20</v>
@@ -9356,7 +9371,7 @@
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B235" s="2">
         <v>46369.708333333336</v>
@@ -9383,7 +9398,7 @@
         <v>18</v>
       </c>
       <c r="J235" s="0" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="K235" s="0" t="s">
         <v>20</v>
@@ -9391,7 +9406,7 @@
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B236" s="2">
         <v>46369.708333333336</v>
@@ -9409,7 +9424,7 @@
         <v>181</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H236" s="0" t="s">
         <v>69</v>
@@ -9418,7 +9433,7 @@
         <v>18</v>
       </c>
       <c r="J236" s="0" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="K236" s="0" t="s">
         <v>20</v>
@@ -9426,7 +9441,7 @@
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B237" s="2">
         <v>46369.708333333336</v>
@@ -9438,7 +9453,7 @@
         <v>34</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F237" s="0" t="s">
         <v>181</v>
@@ -9453,7 +9468,7 @@
         <v>18</v>
       </c>
       <c r="J237" s="0" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="K237" s="0" t="s">
         <v>20</v>
@@ -9461,7 +9476,7 @@
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B238" s="2">
         <v>46369.708333333336</v>
@@ -9488,7 +9503,7 @@
         <v>18</v>
       </c>
       <c r="J238" s="0" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="K238" s="0" t="s">
         <v>20</v>
@@ -9496,7 +9511,7 @@
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B239" s="2">
         <v>46369.708333333336</v>
@@ -9508,22 +9523,22 @@
         <v>34</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F239" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I239" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J239" s="0" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K239" s="0" t="s">
         <v>20</v>
@@ -9531,7 +9546,7 @@
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B240" s="2">
         <v>46369.708333333336</v>
@@ -9543,22 +9558,22 @@
         <v>34</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F240" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I240" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J240" s="0" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K240" s="0" t="s">
         <v>20</v>
@@ -9566,7 +9581,7 @@
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B241" s="2">
         <v>46369.708333333336</v>
@@ -9578,13 +9593,13 @@
         <v>34</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F241" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H241" s="0" t="s">
         <v>77</v>
@@ -9593,7 +9608,7 @@
         <v>18</v>
       </c>
       <c r="J241" s="0" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K241" s="0" t="s">
         <v>20</v>

--- a/data/kamper_2026.xlsx
+++ b/data/kamper_2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="364">
   <si>
     <t>Runde</t>
   </si>
@@ -119,6 +119,18 @@
     <t>17:00</t>
   </si>
   <si>
+    <t>KFUM</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>KFUM-Arena</t>
+  </si>
+  <si>
+    <t>99120001002</t>
+  </si>
+  <si>
     <t>Vålerenga</t>
   </si>
   <si>
@@ -149,18 +161,6 @@
     <t>99120001008</t>
   </si>
   <si>
-    <t>KFUM</t>
-  </si>
-  <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>KFUM-Arena</t>
-  </si>
-  <si>
-    <t>99120001002</t>
-  </si>
-  <si>
     <t>19:15</t>
   </si>
   <si>
@@ -368,12 +368,12 @@
     <t>99120001037</t>
   </si>
   <si>
+    <t>99120001034</t>
+  </si>
+  <si>
     <t>99120001035</t>
   </si>
   <si>
-    <t>99120001034</t>
-  </si>
-  <si>
     <t>99120001038</t>
   </si>
   <si>
@@ -512,12 +512,12 @@
     <t>99120001079</t>
   </si>
   <si>
+    <t>99120001075</t>
+  </si>
+  <si>
     <t>99120001074</t>
   </si>
   <si>
-    <t>99120001075</t>
-  </si>
-  <si>
     <t>99120001078</t>
   </si>
   <si>
@@ -530,24 +530,24 @@
     <t>11</t>
   </si>
   <si>
+    <t>99120001081</t>
+  </si>
+  <si>
     <t>99120001087</t>
   </si>
   <si>
-    <t>99120001081</t>
-  </si>
-  <si>
     <t>99120001082</t>
   </si>
   <si>
+    <t>99120001083</t>
+  </si>
+  <si>
     <t>99120001086</t>
   </si>
   <si>
     <t>99120001088</t>
   </si>
   <si>
-    <t>99120001083</t>
-  </si>
-  <si>
     <t>99120001085</t>
   </si>
   <si>
@@ -560,30 +560,30 @@
     <t>-</t>
   </si>
   <si>
+    <t>99120001089</t>
+  </si>
+  <si>
+    <t>99120001090</t>
+  </si>
+  <si>
+    <t>99120001096</t>
+  </si>
+  <si>
+    <t>99120001091</t>
+  </si>
+  <si>
     <t>99120001092</t>
   </si>
   <si>
     <t>99120001095</t>
   </si>
   <si>
-    <t>99120001096</t>
-  </si>
-  <si>
-    <t>99120001091</t>
-  </si>
-  <si>
-    <t>99120001089</t>
-  </si>
-  <si>
-    <t>99120001090</t>
+    <t>99120001094</t>
   </si>
   <si>
     <t>99120001093</t>
   </si>
   <si>
-    <t>99120001094</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
@@ -629,12 +629,12 @@
     <t>99120001106</t>
   </si>
   <si>
+    <t>99120001108</t>
+  </si>
+  <si>
     <t>99120001110</t>
   </si>
   <si>
-    <t>99120001108</t>
-  </si>
-  <si>
     <t>99120001107</t>
   </si>
   <si>
@@ -656,18 +656,18 @@
     <t>99120001113</t>
   </si>
   <si>
+    <t>2 - 4</t>
+  </si>
+  <si>
+    <t>99120001114</t>
+  </si>
+  <si>
     <t>99120001117</t>
   </si>
   <si>
     <t>99120001118</t>
   </si>
   <si>
-    <t>2 - 4</t>
-  </si>
-  <si>
-    <t>99120001114</t>
-  </si>
-  <si>
     <t>99120001120</t>
   </si>
   <si>
@@ -692,15 +692,15 @@
     <t>99120001126</t>
   </si>
   <si>
+    <t>99120001124</t>
+  </si>
+  <si>
     <t>3 - 3</t>
   </si>
   <si>
     <t>99120001125</t>
   </si>
   <si>
-    <t>99120001124</t>
-  </si>
-  <si>
     <t>2 - 6</t>
   </si>
   <si>
@@ -836,27 +836,33 @@
     <t>99120001165</t>
   </si>
   <si>
+    <t>5 - 3</t>
+  </si>
+  <si>
     <t>99120001166</t>
   </si>
   <si>
+    <t>8 - 1</t>
+  </si>
+  <si>
     <t>99120001168</t>
   </si>
   <si>
+    <t>99120001167</t>
+  </si>
+  <si>
     <t>99120001164</t>
   </si>
   <si>
-    <t>99120001167</t>
+    <t>99120001163</t>
+  </si>
+  <si>
+    <t>99120001162</t>
   </si>
   <si>
     <t>99120001161</t>
   </si>
   <si>
-    <t>99120001163</t>
-  </si>
-  <si>
-    <t>99120001162</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -887,45 +893,48 @@
     <t>23</t>
   </si>
   <si>
+    <t>99120001178</t>
+  </si>
+  <si>
+    <t>99120001177</t>
+  </si>
+  <si>
+    <t>99120001182</t>
+  </si>
+  <si>
+    <t>99120001179</t>
+  </si>
+  <si>
+    <t>99120001183</t>
+  </si>
+  <si>
+    <t>99120001184</t>
+  </si>
+  <si>
+    <t>99120001181</t>
+  </si>
+  <si>
     <t>99120001180</t>
   </si>
   <si>
-    <t>99120001181</t>
-  </si>
-  <si>
-    <t>99120001177</t>
-  </si>
-  <si>
-    <t>99120001178</t>
-  </si>
-  <si>
-    <t>99120001179</t>
-  </si>
-  <si>
-    <t>99120001182</t>
-  </si>
-  <si>
-    <t>99120001183</t>
-  </si>
-  <si>
-    <t>99120001184</t>
-  </si>
-  <si>
     <t>24</t>
   </si>
   <si>
+    <t>99120001185</t>
+  </si>
+  <si>
     <t>99120001186</t>
   </si>
   <si>
+    <t>99120001191</t>
+  </si>
+  <si>
+    <t>99120001189</t>
+  </si>
+  <si>
     <t>99120001192</t>
   </si>
   <si>
-    <t>99120001189</t>
-  </si>
-  <si>
-    <t>99120001185</t>
-  </si>
-  <si>
     <t>99120001187</t>
   </si>
   <si>
@@ -935,166 +944,163 @@
     <t>99120001190</t>
   </si>
   <si>
-    <t>99120001191</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
+    <t>99120001193</t>
+  </si>
+  <si>
+    <t>99120001195</t>
+  </si>
+  <si>
+    <t>99120001200</t>
+  </si>
+  <si>
+    <t>99120001194</t>
+  </si>
+  <si>
     <t>99120001197</t>
   </si>
   <si>
+    <t>99120001196</t>
+  </si>
+  <si>
+    <t>99120001198</t>
+  </si>
+  <si>
     <t>99120001199</t>
   </si>
   <si>
-    <t>99120001193</t>
-  </si>
-  <si>
-    <t>99120001194</t>
-  </si>
-  <si>
-    <t>99120001195</t>
-  </si>
-  <si>
-    <t>99120001196</t>
-  </si>
-  <si>
-    <t>99120001198</t>
-  </si>
-  <si>
-    <t>99120001200</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
+    <t>99120001203</t>
+  </si>
+  <si>
     <t>99120001205</t>
   </si>
   <si>
+    <t>99120001207</t>
+  </si>
+  <si>
     <t>99120001208</t>
   </si>
   <si>
     <t>99120001206</t>
   </si>
   <si>
+    <t>99120001204</t>
+  </si>
+  <si>
+    <t>99120001202</t>
+  </si>
+  <si>
     <t>99120001201</t>
   </si>
   <si>
-    <t>99120001202</t>
-  </si>
-  <si>
-    <t>99120001203</t>
-  </si>
-  <si>
-    <t>99120001204</t>
-  </si>
-  <si>
-    <t>99120001207</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
+    <t>99120001212</t>
+  </si>
+  <si>
+    <t>99120001214</t>
+  </si>
+  <si>
+    <t>99120001209</t>
+  </si>
+  <si>
+    <t>99120001215</t>
+  </si>
+  <si>
+    <t>99120001211</t>
+  </si>
+  <si>
+    <t>99120001216</t>
+  </si>
+  <si>
+    <t>99120001210</t>
+  </si>
+  <si>
     <t>99120001213</t>
   </si>
   <si>
-    <t>99120001214</t>
-  </si>
-  <si>
-    <t>99120001209</t>
-  </si>
-  <si>
-    <t>99120001211</t>
-  </si>
-  <si>
-    <t>99120001210</t>
-  </si>
-  <si>
-    <t>99120001212</t>
-  </si>
-  <si>
-    <t>99120001215</t>
-  </si>
-  <si>
-    <t>99120001216</t>
-  </si>
-  <si>
     <t>28</t>
   </si>
   <si>
+    <t>99120001217</t>
+  </si>
+  <si>
+    <t>99120001221</t>
+  </si>
+  <si>
+    <t>99120001219</t>
+  </si>
+  <si>
     <t>99120001218</t>
   </si>
   <si>
-    <t>99120001221</t>
-  </si>
-  <si>
     <t>99120001222</t>
   </si>
   <si>
     <t>99120001223</t>
   </si>
   <si>
-    <t>99120001217</t>
-  </si>
-  <si>
-    <t>99120001219</t>
+    <t>99120001224</t>
   </si>
   <si>
     <t>99120001220</t>
   </si>
   <si>
-    <t>99120001224</t>
-  </si>
-  <si>
     <t>29</t>
   </si>
   <si>
+    <t>99120001228</t>
+  </si>
+  <si>
     <t>99120001232</t>
   </si>
   <si>
+    <t>99120001231</t>
+  </si>
+  <si>
+    <t>99120001229</t>
+  </si>
+  <si>
+    <t>99120001226</t>
+  </si>
+  <si>
+    <t>99120001227</t>
+  </si>
+  <si>
+    <t>99120001230</t>
+  </si>
+  <si>
     <t>99120001225</t>
   </si>
   <si>
-    <t>99120001226</t>
-  </si>
-  <si>
-    <t>99120001227</t>
-  </si>
-  <si>
-    <t>99120001228</t>
-  </si>
-  <si>
-    <t>99120001229</t>
-  </si>
-  <si>
-    <t>99120001230</t>
-  </si>
-  <si>
-    <t>99120001231</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
+    <t>99120001235</t>
+  </si>
+  <si>
+    <t>99120001237</t>
+  </si>
+  <si>
+    <t>99120001239</t>
+  </si>
+  <si>
+    <t>99120001240</t>
+  </si>
+  <si>
     <t>99120001233</t>
   </si>
   <si>
-    <t>99120001235</t>
-  </si>
-  <si>
-    <t>99120001237</t>
-  </si>
-  <si>
-    <t>99120001239</t>
-  </si>
-  <si>
-    <t>99120001240</t>
+    <t>99120001234</t>
   </si>
   <si>
     <t>99120001236</t>
-  </si>
-  <si>
-    <t>99120001234</t>
   </si>
   <si>
     <t>99120001238</t>
@@ -1336,19 +1342,19 @@
         <v>35</v>
       </c>
       <c r="F5" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="H5" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="I5" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="0" t="s">
         <v>38</v>
-      </c>
-      <c r="I5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>39</v>
       </c>
       <c r="K5" s="0" t="s">
         <v>20</v>
@@ -1368,22 +1374,22 @@
         <v>34</v>
       </c>
       <c r="E6" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="G6" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="H6" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="I6" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="0" t="s">
         <v>43</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>44</v>
       </c>
       <c r="K6" s="0" t="s">
         <v>20</v>
@@ -1403,10 +1409,10 @@
         <v>34</v>
       </c>
       <c r="E7" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="0" t="s">
         <v>45</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>23</v>
       </c>
       <c r="G7" s="0" t="s">
         <v>46</v>
@@ -1508,13 +1514,13 @@
         <v>13</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F10" s="0" t="s">
         <v>58</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H10" s="0" t="s">
         <v>63</v>
@@ -1584,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H12" s="0" t="s">
         <v>69</v>
@@ -1619,7 +1625,7 @@
         <v>71</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H13" s="0" t="s">
         <v>72</v>
@@ -1683,7 +1689,7 @@
         <v>34</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F15" s="0" t="s">
         <v>68</v>
@@ -1718,7 +1724,7 @@
         <v>56</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F16" s="0" t="s">
         <v>74</v>
@@ -1788,7 +1794,7 @@
         <v>28</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>86</v>
@@ -1797,7 +1803,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I18" s="0" t="s">
         <v>18</v>
@@ -1864,7 +1870,7 @@
         <v>58</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H20" s="0" t="s">
         <v>60</v>
@@ -1934,7 +1940,7 @@
         <v>86</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>25</v>
@@ -1998,16 +2004,16 @@
         <v>56</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>74</v>
       </c>
       <c r="G24" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" s="0" t="s">
         <v>37</v>
-      </c>
-      <c r="H24" s="0" t="s">
-        <v>47</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>18</v>
@@ -2033,7 +2039,7 @@
         <v>56</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>97</v>
@@ -2042,7 +2048,7 @@
         <v>52</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>18</v>
@@ -2068,13 +2074,13 @@
         <v>100</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H26" s="0" t="s">
         <v>79</v>
@@ -2249,7 +2255,7 @@
         <v>58</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H31" s="0" t="s">
         <v>72</v>
@@ -2278,16 +2284,16 @@
         <v>34</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F32" s="0" t="s">
         <v>108</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I32" s="0" t="s">
         <v>18</v>
@@ -2319,7 +2325,7 @@
         <v>86</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H33" s="0" t="s">
         <v>75</v>
@@ -2354,7 +2360,7 @@
         <v>81</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H34" s="0" t="s">
         <v>82</v>
@@ -2383,7 +2389,7 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F35" s="0" t="s">
         <v>113</v>
@@ -2453,16 +2459,16 @@
         <v>28</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="H37" s="0" t="s">
         <v>42</v>
-      </c>
-      <c r="H37" s="0" t="s">
-        <v>38</v>
       </c>
       <c r="I37" s="0" t="s">
         <v>18</v>
@@ -2523,16 +2529,16 @@
         <v>34</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="H39" s="0" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I39" s="0" t="s">
         <v>18</v>
@@ -2558,16 +2564,16 @@
         <v>34</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H40" s="0" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="I40" s="0" t="s">
         <v>18</v>
@@ -2593,7 +2599,7 @@
         <v>49</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F41" s="0" t="s">
         <v>58</v>
@@ -2704,7 +2710,7 @@
         <v>124</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>25</v>
@@ -2739,7 +2745,7 @@
         <v>71</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H45" s="0" t="s">
         <v>53</v>
@@ -2768,7 +2774,7 @@
         <v>34</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F46" s="0" t="s">
         <v>58</v>
@@ -2777,7 +2783,7 @@
         <v>29</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I46" s="0" t="s">
         <v>18</v>
@@ -2809,7 +2815,7 @@
         <v>15</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H47" s="0" t="s">
         <v>17</v>
@@ -2838,16 +2844,16 @@
         <v>34</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>57</v>
       </c>
       <c r="H48" s="0" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I48" s="0" t="s">
         <v>18</v>
@@ -2873,7 +2879,7 @@
         <v>49</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>68</v>
@@ -2978,7 +2984,7 @@
         <v>28</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F52" s="0" t="s">
         <v>51</v>
@@ -3048,13 +3054,13 @@
         <v>34</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H54" s="0" t="s">
         <v>77</v>
@@ -3083,7 +3089,7 @@
         <v>34</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F55" s="0" t="s">
         <v>58</v>
@@ -3118,16 +3124,16 @@
         <v>49</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F56" s="0" t="s">
         <v>108</v>
       </c>
       <c r="G56" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I56" s="0" t="s">
         <v>18</v>
@@ -3191,10 +3197,10 @@
         <v>14</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H58" s="0" t="s">
         <v>17</v>
@@ -3264,7 +3270,7 @@
         <v>23</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H60" s="0" t="s">
         <v>69</v>
@@ -3293,7 +3299,7 @@
         <v>34</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>23</v>
@@ -3363,7 +3369,7 @@
         <v>34</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F63" s="0" t="s">
         <v>68</v>
@@ -3372,7 +3378,7 @@
         <v>16</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I63" s="0" t="s">
         <v>18</v>
@@ -3398,7 +3404,7 @@
         <v>21</v>
       </c>
       <c r="E64" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F64" s="0" t="s">
         <v>148</v>
@@ -3433,7 +3439,7 @@
         <v>150</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>15</v>
@@ -3442,7 +3448,7 @@
         <v>31</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I65" s="0" t="s">
         <v>18</v>
@@ -3474,7 +3480,7 @@
         <v>15</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H66" s="0" t="s">
         <v>75</v>
@@ -3503,13 +3509,13 @@
         <v>13</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F67" s="0" t="s">
         <v>71</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H67" s="0" t="s">
         <v>79</v>
@@ -3544,7 +3550,7 @@
         <v>97</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H68" s="0" t="s">
         <v>69</v>
@@ -3576,7 +3582,7 @@
         <v>22</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G69" s="0" t="s">
         <v>29</v>
@@ -3614,7 +3620,7 @@
         <v>157</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H70" s="0" t="s">
         <v>66</v>
@@ -3713,7 +3719,7 @@
         <v>150</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>30</v>
@@ -3722,7 +3728,7 @@
         <v>57</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>18</v>
@@ -3818,13 +3824,13 @@
         <v>28</v>
       </c>
       <c r="E76" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F76" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H76" s="0" t="s">
         <v>63</v>
@@ -3853,16 +3859,16 @@
         <v>34</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F77" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I77" s="0" t="s">
         <v>18</v>
@@ -3888,16 +3894,16 @@
         <v>34</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F78" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="I78" s="0" t="s">
         <v>18</v>
@@ -3964,7 +3970,7 @@
         <v>58</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H80" s="0" t="s">
         <v>53</v>
@@ -3993,7 +3999,7 @@
         <v>49</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F81" s="0" t="s">
         <v>58</v>
@@ -4028,16 +4034,16 @@
         <v>56</v>
       </c>
       <c r="E82" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="I82" s="0" t="s">
         <v>18</v>
@@ -4063,16 +4069,16 @@
         <v>56</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>18</v>
@@ -4104,7 +4110,7 @@
         <v>15</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H84" s="0" t="s">
         <v>72</v>
@@ -4133,16 +4139,16 @@
         <v>56</v>
       </c>
       <c r="E85" s="0" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F85" s="0" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G85" s="0" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H85" s="0" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="I85" s="0" t="s">
         <v>18</v>
@@ -4168,16 +4174,16 @@
         <v>56</v>
       </c>
       <c r="E86" s="0" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F86" s="0" t="s">
         <v>108</v>
       </c>
       <c r="G86" s="0" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="H86" s="0" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="I86" s="0" t="s">
         <v>18</v>
@@ -4203,13 +4209,13 @@
         <v>56</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G87" s="0" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="H87" s="0" t="s">
         <v>47</v>
@@ -4244,7 +4250,7 @@
         <v>15</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H88" s="0" t="s">
         <v>25</v>
@@ -4273,7 +4279,7 @@
         <v>56</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F89" s="0" t="s">
         <v>74</v>
@@ -4299,25 +4305,25 @@
         <v>180</v>
       </c>
       <c r="B90" s="2">
-        <v>46320.708333333336</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="C90" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E90" s="0" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F90" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H90" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I90" s="0" t="s">
         <v>18</v>
@@ -4334,25 +4340,25 @@
         <v>180</v>
       </c>
       <c r="B91" s="2">
-        <v>46320.708333333336</v>
+        <v>46319.75</v>
       </c>
       <c r="C91" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E91" s="0" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F91" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G91" s="0" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H91" s="0" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="I91" s="0" t="s">
         <v>18</v>
@@ -4369,13 +4375,13 @@
         <v>180</v>
       </c>
       <c r="B92" s="2">
-        <v>46320.708333333336</v>
+        <v>46320.604166666664</v>
       </c>
       <c r="C92" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E92" s="0" t="s">
         <v>16</v>
@@ -4419,7 +4425,7 @@
         <v>181</v>
       </c>
       <c r="G93" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H93" s="0" t="s">
         <v>32</v>
@@ -4448,16 +4454,16 @@
         <v>34</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F94" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G94" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H94" s="0" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I94" s="0" t="s">
         <v>18</v>
@@ -4483,16 +4489,16 @@
         <v>34</v>
       </c>
       <c r="E95" s="0" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F95" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H95" s="0" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="I95" s="0" t="s">
         <v>18</v>
@@ -4518,16 +4524,16 @@
         <v>34</v>
       </c>
       <c r="E96" s="0" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="F96" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H96" s="0" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I96" s="0" t="s">
         <v>18</v>
@@ -4544,25 +4550,25 @@
         <v>180</v>
       </c>
       <c r="B97" s="2">
-        <v>46320.708333333336</v>
+        <v>46320.802083333336</v>
       </c>
       <c r="C97" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E97" s="0" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="F97" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G97" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H97" s="0" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I97" s="0" t="s">
         <v>18</v>
@@ -4594,7 +4600,7 @@
         <v>68</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H98" s="0" t="s">
         <v>72</v>
@@ -4623,7 +4629,7 @@
         <v>13</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F99" s="0" t="s">
         <v>108</v>
@@ -4632,7 +4638,7 @@
         <v>22</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I99" s="0" t="s">
         <v>18</v>
@@ -4664,7 +4670,7 @@
         <v>51</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H100" s="0" t="s">
         <v>53</v>
@@ -4693,7 +4699,7 @@
         <v>28</v>
       </c>
       <c r="E101" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F101" s="0" t="s">
         <v>68</v>
@@ -4702,7 +4708,7 @@
         <v>59</v>
       </c>
       <c r="H101" s="0" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I101" s="0" t="s">
         <v>18</v>
@@ -4734,7 +4740,7 @@
         <v>15</v>
       </c>
       <c r="G102" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H102" s="0" t="s">
         <v>75</v>
@@ -4763,7 +4769,7 @@
         <v>34</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F103" s="0" t="s">
         <v>108</v>
@@ -4836,7 +4842,7 @@
         <v>57</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>16</v>
@@ -4868,16 +4874,16 @@
         <v>56</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F106" s="0" t="s">
         <v>201</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I106" s="0" t="s">
         <v>18</v>
@@ -4906,7 +4912,7 @@
         <v>59</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>52</v>
@@ -4976,13 +4982,13 @@
         <v>46</v>
       </c>
       <c r="F109" s="0" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="G109" s="0" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="H109" s="0" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I109" s="0" t="s">
         <v>18</v>
@@ -5008,16 +5014,16 @@
         <v>13</v>
       </c>
       <c r="E110" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F110" s="0" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="G110" s="0" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H110" s="0" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="I110" s="0" t="s">
         <v>18</v>
@@ -5119,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H113" s="0" t="s">
         <v>66</v>
@@ -5154,7 +5160,7 @@
         <v>113</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H114" s="0" t="s">
         <v>53</v>
@@ -5189,7 +5195,7 @@
         <v>74</v>
       </c>
       <c r="G115" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H115" s="0" t="s">
         <v>32</v>
@@ -5224,7 +5230,7 @@
         <v>97</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H116" s="0" t="s">
         <v>75</v>
@@ -5253,22 +5259,22 @@
         <v>34</v>
       </c>
       <c r="E117" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="F117" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="G117" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="H117" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="F117" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="G117" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="H117" s="0" t="s">
-        <v>77</v>
-      </c>
       <c r="I117" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J117" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K117" s="0" t="s">
         <v>20</v>
@@ -5288,22 +5294,22 @@
         <v>34</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F118" s="0" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="G118" s="0" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="I118" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J118" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K118" s="0" t="s">
         <v>20</v>
@@ -5323,16 +5329,16 @@
         <v>34</v>
       </c>
       <c r="E119" s="0" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>216</v>
+        <v>40</v>
       </c>
       <c r="G119" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H119" s="0" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>18</v>
@@ -5358,7 +5364,7 @@
         <v>49</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F120" s="0" t="s">
         <v>58</v>
@@ -5367,7 +5373,7 @@
         <v>16</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I120" s="0" t="s">
         <v>18</v>
@@ -5428,7 +5434,7 @@
         <v>56</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F122" s="0" t="s">
         <v>88</v>
@@ -5437,7 +5443,7 @@
         <v>14</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I122" s="0" t="s">
         <v>18</v>
@@ -5469,7 +5475,7 @@
         <v>51</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H123" s="0" t="s">
         <v>82</v>
@@ -5501,10 +5507,10 @@
         <v>52</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H124" s="0" t="s">
         <v>72</v>
@@ -5533,7 +5539,7 @@
         <v>21</v>
       </c>
       <c r="E125" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F125" s="0" t="s">
         <v>88</v>
@@ -5568,22 +5574,22 @@
         <v>34</v>
       </c>
       <c r="E126" s="0" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F126" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="G126" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="H126" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="I126" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J126" s="0" t="s">
         <v>226</v>
-      </c>
-      <c r="G126" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="H126" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="I126" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="J126" s="0" t="s">
-        <v>227</v>
       </c>
       <c r="K126" s="0" t="s">
         <v>20</v>
@@ -5603,16 +5609,16 @@
         <v>34</v>
       </c>
       <c r="E127" s="0" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F127" s="0" t="s">
-        <v>15</v>
+        <v>227</v>
       </c>
       <c r="G127" s="0" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="H127" s="0" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>18</v>
@@ -5638,7 +5644,7 @@
         <v>34</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F128" s="0" t="s">
         <v>229</v>
@@ -5647,7 +5653,7 @@
         <v>50</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I128" s="0" t="s">
         <v>18</v>
@@ -5743,13 +5749,13 @@
         <v>56</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>86</v>
       </c>
       <c r="G131" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H131" s="0" t="s">
         <v>77</v>
@@ -5778,7 +5784,7 @@
         <v>100</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F132" s="0" t="s">
         <v>74</v>
@@ -5787,7 +5793,7 @@
         <v>59</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I132" s="0" t="s">
         <v>18</v>
@@ -5848,7 +5854,7 @@
         <v>21</v>
       </c>
       <c r="E134" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F134" s="0" t="s">
         <v>86</v>
@@ -5883,7 +5889,7 @@
         <v>28</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F135" s="0" t="s">
         <v>68</v>
@@ -5924,7 +5930,7 @@
         <v>58</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H136" s="0" t="s">
         <v>17</v>
@@ -5994,7 +6000,7 @@
         <v>103</v>
       </c>
       <c r="G138" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H138" s="0" t="s">
         <v>82</v>
@@ -6058,16 +6064,16 @@
         <v>13</v>
       </c>
       <c r="E140" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F140" s="0" t="s">
         <v>58</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H140" s="0" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I140" s="0" t="s">
         <v>18</v>
@@ -6093,16 +6099,16 @@
         <v>28</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F141" s="0" t="s">
         <v>246</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I141" s="0" t="s">
         <v>18</v>
@@ -6169,7 +6175,7 @@
         <v>74</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H143" s="0" t="s">
         <v>60</v>
@@ -6236,7 +6242,7 @@
         <v>52</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>29</v>
@@ -6338,7 +6344,7 @@
         <v>34</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F148" s="0" t="s">
         <v>113</v>
@@ -6408,13 +6414,13 @@
         <v>34</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F150" s="0" t="s">
         <v>65</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H150" s="0" t="s">
         <v>63</v>
@@ -6449,7 +6455,7 @@
         <v>15</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H151" s="0" t="s">
         <v>66</v>
@@ -6478,7 +6484,7 @@
         <v>34</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F152" s="0" t="s">
         <v>260</v>
@@ -6487,7 +6493,7 @@
         <v>22</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>18</v>
@@ -6513,7 +6519,7 @@
         <v>49</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F153" s="0" t="s">
         <v>148</v>
@@ -6548,16 +6554,16 @@
         <v>56</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I154" s="0" t="s">
         <v>18</v>
@@ -6586,7 +6592,7 @@
         <v>52</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="G155" s="0" t="s">
         <v>59</v>
@@ -6618,10 +6624,10 @@
         <v>222</v>
       </c>
       <c r="E156" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F156" s="0" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="G156" s="0" t="s">
         <v>16</v>
@@ -6656,7 +6662,7 @@
         <v>24</v>
       </c>
       <c r="F157" s="0" t="s">
-        <v>181</v>
+        <v>51</v>
       </c>
       <c r="G157" s="0" t="s">
         <v>14</v>
@@ -6691,10 +6697,10 @@
         <v>31</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H158" s="0" t="s">
         <v>75</v>
@@ -6726,10 +6732,10 @@
         <v>57</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H159" s="0" t="s">
         <v>60</v>
@@ -6761,10 +6767,10 @@
         <v>22</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="G160" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H160" s="0" t="s">
         <v>25</v>
@@ -6796,7 +6802,7 @@
         <v>29</v>
       </c>
       <c r="F161" s="0" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="G161" s="0" t="s">
         <v>50</v>
@@ -6828,13 +6834,13 @@
         <v>13</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F162" s="0" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H162" s="0" t="s">
         <v>79</v>
@@ -6866,7 +6872,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="0" t="s">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="G163" s="0" t="s">
         <v>50</v>
@@ -6878,7 +6884,7 @@
         <v>18</v>
       </c>
       <c r="J163" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K163" s="0" t="s">
         <v>20</v>
@@ -6901,7 +6907,7 @@
         <v>16</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>181</v>
+        <v>276</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>29</v>
@@ -6913,7 +6919,7 @@
         <v>18</v>
       </c>
       <c r="J164" s="0" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K164" s="0" t="s">
         <v>20</v>
@@ -6933,22 +6939,22 @@
         <v>34</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="I165" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J165" s="0" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K165" s="0" t="s">
         <v>20</v>
@@ -6968,22 +6974,22 @@
         <v>34</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="G166" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J166" s="0" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K166" s="0" t="s">
         <v>20</v>
@@ -7003,22 +7009,22 @@
         <v>34</v>
       </c>
       <c r="E167" s="0" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="F167" s="0" t="s">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="G167" s="0" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H167" s="0" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I167" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J167" s="0" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K167" s="0" t="s">
         <v>20</v>
@@ -7029,31 +7035,31 @@
         <v>272</v>
       </c>
       <c r="B168" s="2">
-        <v>46278.708333333336</v>
+        <v>46278.802083333336</v>
       </c>
       <c r="C168" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E168" s="0" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F168" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G168" s="0" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="H168" s="0" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="I168" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J168" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K168" s="0" t="s">
         <v>20</v>
@@ -7064,31 +7070,31 @@
         <v>272</v>
       </c>
       <c r="B169" s="2">
-        <v>46278.802083333336</v>
+        <v>46279.791666666664</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E169" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F169" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="H169" s="0" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I169" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J169" s="0" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K169" s="0" t="s">
         <v>20</v>
@@ -7096,7 +7102,7 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B170" s="2">
         <v>46283.791666666664</v>
@@ -7114,7 +7120,7 @@
         <v>181</v>
       </c>
       <c r="G170" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H170" s="0" t="s">
         <v>60</v>
@@ -7123,7 +7129,7 @@
         <v>18</v>
       </c>
       <c r="J170" s="0" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K170" s="0" t="s">
         <v>20</v>
@@ -7131,7 +7137,7 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B171" s="2">
         <v>46284.666666666664</v>
@@ -7158,7 +7164,7 @@
         <v>18</v>
       </c>
       <c r="J171" s="0" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K171" s="0" t="s">
         <v>20</v>
@@ -7166,7 +7172,7 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B172" s="2">
         <v>46284.75</v>
@@ -7184,7 +7190,7 @@
         <v>181</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H172" s="0" t="s">
         <v>25</v>
@@ -7193,7 +7199,7 @@
         <v>18</v>
       </c>
       <c r="J172" s="0" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K172" s="0" t="s">
         <v>20</v>
@@ -7201,7 +7207,7 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B173" s="2">
         <v>46285.604166666664</v>
@@ -7213,7 +7219,7 @@
         <v>28</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F173" s="0" t="s">
         <v>181</v>
@@ -7222,13 +7228,13 @@
         <v>52</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I173" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J173" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K173" s="0" t="s">
         <v>20</v>
@@ -7236,7 +7242,7 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B174" s="2">
         <v>46285.708333333336</v>
@@ -7248,13 +7254,13 @@
         <v>34</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F174" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H174" s="0" t="s">
         <v>77</v>
@@ -7263,7 +7269,7 @@
         <v>18</v>
       </c>
       <c r="J174" s="0" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K174" s="0" t="s">
         <v>20</v>
@@ -7271,7 +7277,7 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B175" s="2">
         <v>46285.708333333336</v>
@@ -7298,7 +7304,7 @@
         <v>18</v>
       </c>
       <c r="J175" s="0" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K175" s="0" t="s">
         <v>20</v>
@@ -7306,7 +7312,7 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B176" s="2">
         <v>46285.708333333336</v>
@@ -7324,7 +7330,7 @@
         <v>181</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H176" s="0" t="s">
         <v>66</v>
@@ -7333,7 +7339,7 @@
         <v>18</v>
       </c>
       <c r="J176" s="0" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K176" s="0" t="s">
         <v>20</v>
@@ -7341,7 +7347,7 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B177" s="2">
         <v>46285.802083333336</v>
@@ -7368,7 +7374,7 @@
         <v>18</v>
       </c>
       <c r="J177" s="0" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K177" s="0" t="s">
         <v>20</v>
@@ -7376,34 +7382,34 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B178" s="2">
-        <v>46306.708333333336</v>
+        <v>46304.791666666664</v>
       </c>
       <c r="C178" s="0" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E178" s="0" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F178" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G178" s="0" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J178" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K178" s="0" t="s">
         <v>20</v>
@@ -7411,34 +7417,34 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B179" s="2">
-        <v>46306.708333333336</v>
+        <v>46305.666666666664</v>
       </c>
       <c r="C179" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E179" s="0" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F179" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G179" s="0" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H179" s="0" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I179" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J179" s="0" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K179" s="0" t="s">
         <v>20</v>
@@ -7446,34 +7452,34 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B180" s="2">
-        <v>46306.708333333336</v>
+        <v>46305.75</v>
       </c>
       <c r="C180" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E180" s="0" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F180" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H180" s="0" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="I180" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J180" s="0" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K180" s="0" t="s">
         <v>20</v>
@@ -7481,34 +7487,34 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B181" s="2">
-        <v>46306.708333333336</v>
+        <v>46306.604166666664</v>
       </c>
       <c r="C181" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E181" s="0" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F181" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G181" s="0" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="H181" s="0" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J181" s="0" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K181" s="0" t="s">
         <v>20</v>
@@ -7516,7 +7522,7 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B182" s="2">
         <v>46306.708333333336</v>
@@ -7528,22 +7534,22 @@
         <v>34</v>
       </c>
       <c r="E182" s="0" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F182" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G182" s="0" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="H182" s="0" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I182" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J182" s="0" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K182" s="0" t="s">
         <v>20</v>
@@ -7551,7 +7557,7 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B183" s="2">
         <v>46306.708333333336</v>
@@ -7563,22 +7569,22 @@
         <v>34</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G183" s="0" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="I183" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J183" s="0" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K183" s="0" t="s">
         <v>20</v>
@@ -7586,16 +7592,16 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B184" s="2">
-        <v>46306.708333333336</v>
+        <v>46306.802083333336</v>
       </c>
       <c r="C184" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E184" s="0" t="s">
         <v>46</v>
@@ -7604,16 +7610,16 @@
         <v>181</v>
       </c>
       <c r="G184" s="0" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H184" s="0" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="I184" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J184" s="0" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K184" s="0" t="s">
         <v>20</v>
@@ -7621,34 +7627,34 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B185" s="2">
-        <v>46306.708333333336</v>
+        <v>46307.791666666664</v>
       </c>
       <c r="C185" s="0" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E185" s="0" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F185" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H185" s="0" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I185" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J185" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K185" s="0" t="s">
         <v>20</v>
@@ -7656,34 +7662,34 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B186" s="2">
-        <v>46313.708333333336</v>
+        <v>46312.583333333336</v>
       </c>
       <c r="C186" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="E186" s="0" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F186" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G186" s="0" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="H186" s="0" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I186" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J186" s="0" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K186" s="0" t="s">
         <v>20</v>
@@ -7691,34 +7697,34 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B187" s="2">
-        <v>46313.708333333336</v>
+        <v>46312.666666666664</v>
       </c>
       <c r="C187" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E187" s="0" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F187" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H187" s="0" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I187" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J187" s="0" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K187" s="0" t="s">
         <v>20</v>
@@ -7726,34 +7732,34 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B188" s="2">
-        <v>46313.708333333336</v>
+        <v>46312.75</v>
       </c>
       <c r="C188" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E188" s="0" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="F188" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G188" s="0" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="H188" s="0" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I188" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J188" s="0" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K188" s="0" t="s">
         <v>20</v>
@@ -7761,34 +7767,34 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B189" s="2">
-        <v>46313.708333333336</v>
+        <v>46313.604166666664</v>
       </c>
       <c r="C189" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E189" s="0" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="F189" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G189" s="0" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="H189" s="0" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="I189" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J189" s="0" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K189" s="0" t="s">
         <v>20</v>
@@ -7796,7 +7802,7 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B190" s="2">
         <v>46313.708333333336</v>
@@ -7808,22 +7814,22 @@
         <v>34</v>
       </c>
       <c r="E190" s="0" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F190" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G190" s="0" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="I190" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J190" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K190" s="0" t="s">
         <v>20</v>
@@ -7831,7 +7837,7 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B191" s="2">
         <v>46313.708333333336</v>
@@ -7843,22 +7849,22 @@
         <v>34</v>
       </c>
       <c r="E191" s="0" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F191" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G191" s="0" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H191" s="0" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="I191" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J191" s="0" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K191" s="0" t="s">
         <v>20</v>
@@ -7866,7 +7872,7 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B192" s="2">
         <v>46313.708333333336</v>
@@ -7878,22 +7884,22 @@
         <v>34</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F192" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J192" s="0" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K192" s="0" t="s">
         <v>20</v>
@@ -7901,34 +7907,34 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B193" s="2">
-        <v>46313.708333333336</v>
+        <v>46313.802083333336</v>
       </c>
       <c r="C193" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E193" s="0" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="F193" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G193" s="0" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="H193" s="0" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="I193" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J193" s="0" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K193" s="0" t="s">
         <v>20</v>
@@ -7936,34 +7942,34 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B194" s="2">
-        <v>46327.708333333336</v>
+        <v>46325.791666666664</v>
       </c>
       <c r="C194" s="0" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E194" s="0" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F194" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G194" s="0" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H194" s="0" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="I194" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J194" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K194" s="0" t="s">
         <v>20</v>
@@ -7971,34 +7977,34 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B195" s="2">
-        <v>46327.708333333336</v>
+        <v>46326.666666666664</v>
       </c>
       <c r="C195" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E195" s="0" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F195" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G195" s="0" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="H195" s="0" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J195" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K195" s="0" t="s">
         <v>20</v>
@@ -8006,34 +8012,34 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B196" s="2">
-        <v>46327.708333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="C196" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F196" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J196" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K196" s="0" t="s">
         <v>20</v>
@@ -8041,16 +8047,16 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B197" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.604166666664</v>
       </c>
       <c r="C197" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E197" s="0" t="s">
         <v>31</v>
@@ -8068,7 +8074,7 @@
         <v>18</v>
       </c>
       <c r="J197" s="0" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K197" s="0" t="s">
         <v>20</v>
@@ -8076,7 +8082,7 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B198" s="2">
         <v>46327.708333333336</v>
@@ -8088,22 +8094,22 @@
         <v>34</v>
       </c>
       <c r="E198" s="0" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F198" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G198" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H198" s="0" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J198" s="0" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K198" s="0" t="s">
         <v>20</v>
@@ -8111,7 +8117,7 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B199" s="2">
         <v>46327.708333333336</v>
@@ -8123,7 +8129,7 @@
         <v>34</v>
       </c>
       <c r="E199" s="0" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F199" s="0" t="s">
         <v>181</v>
@@ -8132,13 +8138,13 @@
         <v>14</v>
       </c>
       <c r="H199" s="0" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I199" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J199" s="0" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K199" s="0" t="s">
         <v>20</v>
@@ -8146,7 +8152,7 @@
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B200" s="2">
         <v>46327.708333333336</v>
@@ -8158,13 +8164,13 @@
         <v>34</v>
       </c>
       <c r="E200" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F200" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H200" s="0" t="s">
         <v>63</v>
@@ -8173,7 +8179,7 @@
         <v>18</v>
       </c>
       <c r="J200" s="0" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K200" s="0" t="s">
         <v>20</v>
@@ -8181,34 +8187,34 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B201" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.802083333336</v>
       </c>
       <c r="C201" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F201" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G201" s="0" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I201" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J201" s="0" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K201" s="0" t="s">
         <v>20</v>
@@ -8216,34 +8222,34 @@
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B202" s="2">
-        <v>46334.708333333336</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="C202" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E202" s="0" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F202" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="H202" s="0" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="I202" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J202" s="0" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K202" s="0" t="s">
         <v>20</v>
@@ -8251,34 +8257,34 @@
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B203" s="2">
-        <v>46334.708333333336</v>
+        <v>46333.75</v>
       </c>
       <c r="C203" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E203" s="0" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F203" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G203" s="0" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H203" s="0" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I203" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J203" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K203" s="0" t="s">
         <v>20</v>
@@ -8286,34 +8292,34 @@
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B204" s="2">
-        <v>46334.708333333336</v>
+        <v>46334.604166666664</v>
       </c>
       <c r="C204" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E204" s="0" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F204" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G204" s="0" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="H204" s="0" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I204" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J204" s="0" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K204" s="0" t="s">
         <v>20</v>
@@ -8321,7 +8327,7 @@
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B205" s="2">
         <v>46334.708333333336</v>
@@ -8333,22 +8339,22 @@
         <v>34</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F205" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I205" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J205" s="0" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K205" s="0" t="s">
         <v>20</v>
@@ -8356,7 +8362,7 @@
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B206" s="2">
         <v>46334.708333333336</v>
@@ -8368,22 +8374,22 @@
         <v>34</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F206" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G206" s="0" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="I206" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J206" s="0" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K206" s="0" t="s">
         <v>20</v>
@@ -8391,7 +8397,7 @@
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B207" s="2">
         <v>46334.708333333336</v>
@@ -8403,22 +8409,22 @@
         <v>34</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F207" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="I207" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J207" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K207" s="0" t="s">
         <v>20</v>
@@ -8426,7 +8432,7 @@
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B208" s="2">
         <v>46334.708333333336</v>
@@ -8438,22 +8444,22 @@
         <v>34</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F208" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="I208" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J208" s="0" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K208" s="0" t="s">
         <v>20</v>
@@ -8461,34 +8467,34 @@
     </row>
     <row r="209">
       <c r="A209" s="0" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B209" s="2">
-        <v>46334.708333333336</v>
+        <v>46334.802083333336</v>
       </c>
       <c r="C209" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F209" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="I209" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J209" s="0" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K209" s="0" t="s">
         <v>20</v>
@@ -8496,34 +8502,34 @@
     </row>
     <row r="210">
       <c r="A210" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B210" s="2">
-        <v>46348.708333333336</v>
+        <v>46346.791666666664</v>
       </c>
       <c r="C210" s="0" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="F210" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I210" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J210" s="0" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K210" s="0" t="s">
         <v>20</v>
@@ -8531,16 +8537,16 @@
     </row>
     <row r="211">
       <c r="A211" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B211" s="2">
-        <v>46348.708333333336</v>
+        <v>46347.583333333336</v>
       </c>
       <c r="C211" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="E211" s="0" t="s">
         <v>50</v>
@@ -8558,7 +8564,7 @@
         <v>18</v>
       </c>
       <c r="J211" s="0" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K211" s="0" t="s">
         <v>20</v>
@@ -8566,16 +8572,16 @@
     </row>
     <row r="212">
       <c r="A212" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B212" s="2">
-        <v>46348.708333333336</v>
+        <v>46347.666666666664</v>
       </c>
       <c r="C212" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E212" s="0" t="s">
         <v>14</v>
@@ -8593,7 +8599,7 @@
         <v>18</v>
       </c>
       <c r="J212" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K212" s="0" t="s">
         <v>20</v>
@@ -8601,34 +8607,34 @@
     </row>
     <row r="213">
       <c r="A213" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B213" s="2">
-        <v>46348.708333333336</v>
+        <v>46347.75</v>
       </c>
       <c r="C213" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F213" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G213" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I213" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J213" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K213" s="0" t="s">
         <v>20</v>
@@ -8636,7 +8642,7 @@
     </row>
     <row r="214">
       <c r="A214" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B214" s="2">
         <v>46348.708333333336</v>
@@ -8648,22 +8654,22 @@
         <v>34</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="F214" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G214" s="0" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I214" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J214" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K214" s="0" t="s">
         <v>20</v>
@@ -8671,7 +8677,7 @@
     </row>
     <row r="215">
       <c r="A215" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B215" s="2">
         <v>46348.708333333336</v>
@@ -8683,22 +8689,22 @@
         <v>34</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F215" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="I215" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J215" s="0" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K215" s="0" t="s">
         <v>20</v>
@@ -8706,7 +8712,7 @@
     </row>
     <row r="216">
       <c r="A216" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B216" s="2">
         <v>46348.708333333336</v>
@@ -8724,16 +8730,16 @@
         <v>181</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I216" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J216" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K216" s="0" t="s">
         <v>20</v>
@@ -8741,34 +8747,34 @@
     </row>
     <row r="217">
       <c r="A217" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B217" s="2">
-        <v>46348.708333333336</v>
+        <v>46348.802083333336</v>
       </c>
       <c r="C217" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F217" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="H217" s="0" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="I217" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J217" s="0" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K217" s="0" t="s">
         <v>20</v>
@@ -8776,34 +8782,34 @@
     </row>
     <row r="218">
       <c r="A218" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B218" s="2">
-        <v>46355.708333333336</v>
+        <v>46354.666666666664</v>
       </c>
       <c r="C218" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="F218" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I218" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J218" s="0" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K218" s="0" t="s">
         <v>20</v>
@@ -8811,16 +8817,16 @@
     </row>
     <row r="219">
       <c r="A219" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B219" s="2">
-        <v>46355.708333333336</v>
+        <v>46354.75</v>
       </c>
       <c r="C219" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E219" s="0" t="s">
         <v>24</v>
@@ -8838,7 +8844,7 @@
         <v>18</v>
       </c>
       <c r="J219" s="0" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K219" s="0" t="s">
         <v>20</v>
@@ -8846,34 +8852,34 @@
     </row>
     <row r="220">
       <c r="A220" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B220" s="2">
-        <v>46355.708333333336</v>
+        <v>46355.604166666664</v>
       </c>
       <c r="C220" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F220" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H220" s="0" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J220" s="0" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K220" s="0" t="s">
         <v>20</v>
@@ -8881,7 +8887,7 @@
     </row>
     <row r="221">
       <c r="A221" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B221" s="2">
         <v>46355.708333333336</v>
@@ -8893,22 +8899,22 @@
         <v>34</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F221" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G221" s="0" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="I221" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J221" s="0" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K221" s="0" t="s">
         <v>20</v>
@@ -8916,7 +8922,7 @@
     </row>
     <row r="222">
       <c r="A222" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B222" s="2">
         <v>46355.708333333336</v>
@@ -8928,22 +8934,22 @@
         <v>34</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="F222" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I222" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J222" s="0" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K222" s="0" t="s">
         <v>20</v>
@@ -8951,7 +8957,7 @@
     </row>
     <row r="223">
       <c r="A223" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B223" s="2">
         <v>46355.708333333336</v>
@@ -8963,22 +8969,22 @@
         <v>34</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F223" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I223" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J223" s="0" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K223" s="0" t="s">
         <v>20</v>
@@ -8986,34 +8992,34 @@
     </row>
     <row r="224">
       <c r="A224" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B224" s="2">
-        <v>46355.708333333336</v>
+        <v>46355.802083333336</v>
       </c>
       <c r="C224" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="F224" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H224" s="0" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="I224" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J224" s="0" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K224" s="0" t="s">
         <v>20</v>
@@ -9021,34 +9027,34 @@
     </row>
     <row r="225">
       <c r="A225" s="0" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B225" s="2">
-        <v>46355.708333333336</v>
+        <v>46356.791666666664</v>
       </c>
       <c r="C225" s="0" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F225" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G225" s="0" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H225" s="0" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I225" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J225" s="0" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K225" s="0" t="s">
         <v>20</v>
@@ -9056,34 +9062,34 @@
     </row>
     <row r="226">
       <c r="A226" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B226" s="2">
-        <v>46362.708333333336</v>
+        <v>46360.791666666664</v>
       </c>
       <c r="C226" s="0" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F226" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G226" s="0" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="I226" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J226" s="0" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K226" s="0" t="s">
         <v>20</v>
@@ -9091,34 +9097,34 @@
     </row>
     <row r="227">
       <c r="A227" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B227" s="2">
-        <v>46362.708333333336</v>
+        <v>46361.666666666664</v>
       </c>
       <c r="C227" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F227" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I227" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J227" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K227" s="0" t="s">
         <v>20</v>
@@ -9126,34 +9132,34 @@
     </row>
     <row r="228">
       <c r="A228" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B228" s="2">
-        <v>46362.708333333336</v>
+        <v>46361.75</v>
       </c>
       <c r="C228" s="0" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F228" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I228" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J228" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K228" s="0" t="s">
         <v>20</v>
@@ -9161,34 +9167,34 @@
     </row>
     <row r="229">
       <c r="A229" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B229" s="2">
-        <v>46362.708333333336</v>
+        <v>46362.604166666664</v>
       </c>
       <c r="C229" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="F229" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="I229" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J229" s="0" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K229" s="0" t="s">
         <v>20</v>
@@ -9196,7 +9202,7 @@
     </row>
     <row r="230">
       <c r="A230" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B230" s="2">
         <v>46362.708333333336</v>
@@ -9208,22 +9214,22 @@
         <v>34</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F230" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I230" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J230" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K230" s="0" t="s">
         <v>20</v>
@@ -9231,7 +9237,7 @@
     </row>
     <row r="231">
       <c r="A231" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B231" s="2">
         <v>46362.708333333336</v>
@@ -9243,22 +9249,22 @@
         <v>34</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="F231" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="I231" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J231" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="K231" s="0" t="s">
         <v>20</v>
@@ -9266,7 +9272,7 @@
     </row>
     <row r="232">
       <c r="A232" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B232" s="2">
         <v>46362.708333333336</v>
@@ -9284,7 +9290,7 @@
         <v>181</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H232" s="0" t="s">
         <v>53</v>
@@ -9293,7 +9299,7 @@
         <v>18</v>
       </c>
       <c r="J232" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K232" s="0" t="s">
         <v>20</v>
@@ -9301,34 +9307,34 @@
     </row>
     <row r="233">
       <c r="A233" s="0" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B233" s="2">
-        <v>46362.708333333336</v>
+        <v>46362.802083333336</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>27</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F233" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I233" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J233" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K233" s="0" t="s">
         <v>20</v>
@@ -9336,7 +9342,7 @@
     </row>
     <row r="234">
       <c r="A234" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B234" s="2">
         <v>46369.708333333336</v>
@@ -9348,22 +9354,22 @@
         <v>34</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F234" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="I234" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J234" s="0" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K234" s="0" t="s">
         <v>20</v>
@@ -9371,7 +9377,7 @@
     </row>
     <row r="235">
       <c r="A235" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B235" s="2">
         <v>46369.708333333336</v>
@@ -9383,22 +9389,22 @@
         <v>34</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F235" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="I235" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J235" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K235" s="0" t="s">
         <v>20</v>
@@ -9406,7 +9412,7 @@
     </row>
     <row r="236">
       <c r="A236" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B236" s="2">
         <v>46369.708333333336</v>
@@ -9418,22 +9424,22 @@
         <v>34</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F236" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I236" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J236" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K236" s="0" t="s">
         <v>20</v>
@@ -9441,7 +9447,7 @@
     </row>
     <row r="237">
       <c r="A237" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B237" s="2">
         <v>46369.708333333336</v>
@@ -9453,22 +9459,22 @@
         <v>34</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="F237" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I237" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J237" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K237" s="0" t="s">
         <v>20</v>
@@ -9476,7 +9482,7 @@
     </row>
     <row r="238">
       <c r="A238" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B238" s="2">
         <v>46369.708333333336</v>
@@ -9488,22 +9494,22 @@
         <v>34</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="F238" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G238" s="0" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I238" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J238" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K238" s="0" t="s">
         <v>20</v>
@@ -9511,7 +9517,7 @@
     </row>
     <row r="239">
       <c r="A239" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B239" s="2">
         <v>46369.708333333336</v>
@@ -9523,22 +9529,22 @@
         <v>34</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F239" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I239" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J239" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K239" s="0" t="s">
         <v>20</v>
@@ -9546,7 +9552,7 @@
     </row>
     <row r="240">
       <c r="A240" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B240" s="2">
         <v>46369.708333333336</v>
@@ -9558,22 +9564,22 @@
         <v>34</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F240" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="I240" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J240" s="0" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K240" s="0" t="s">
         <v>20</v>
@@ -9581,7 +9587,7 @@
     </row>
     <row r="241">
       <c r="A241" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B241" s="2">
         <v>46369.708333333336</v>
@@ -9593,13 +9599,13 @@
         <v>34</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F241" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H241" s="0" t="s">
         <v>77</v>
@@ -9608,7 +9614,7 @@
         <v>18</v>
       </c>
       <c r="J241" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K241" s="0" t="s">
         <v>20</v>

--- a/data/kamper_2026.xlsx
+++ b/data/kamper_2026.xlsx
@@ -131,6 +131,21 @@
     <t>99120001002</t>
   </si>
   <si>
+    <t>Aalesund</t>
+  </si>
+  <si>
+    <t>1 - 3</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
+    <t>Color Line Stadion</t>
+  </si>
+  <si>
+    <t>99120001008</t>
+  </si>
+  <si>
     <t>Vålerenga</t>
   </si>
   <si>
@@ -146,21 +161,6 @@
     <t>99120001007</t>
   </si>
   <si>
-    <t>Aalesund</t>
-  </si>
-  <si>
-    <t>1 - 3</t>
-  </si>
-  <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Color Line Stadion</t>
-  </si>
-  <si>
-    <t>99120001008</t>
-  </si>
-  <si>
     <t>19:15</t>
   </si>
   <si>
@@ -236,6 +236,12 @@
     <t>99120001011</t>
   </si>
   <si>
+    <t>Jotun Arena</t>
+  </si>
+  <si>
+    <t>99120001014</t>
+  </si>
+  <si>
     <t>1 - 2</t>
   </si>
   <si>
@@ -245,12 +251,6 @@
     <t>99120001010</t>
   </si>
   <si>
-    <t>Jotun Arena</t>
-  </si>
-  <si>
-    <t>99120001014</t>
-  </si>
-  <si>
     <t>Åråsen stadion</t>
   </si>
   <si>
@@ -335,15 +335,15 @@
     <t>99120001028</t>
   </si>
   <si>
+    <t>2 - 2</t>
+  </si>
+  <si>
+    <t>99120001032</t>
+  </si>
+  <si>
     <t>99120001026</t>
   </si>
   <si>
-    <t>2 - 2</t>
-  </si>
-  <si>
-    <t>99120001032</t>
-  </si>
-  <si>
     <t>99120001025</t>
   </si>
   <si>
@@ -482,18 +482,18 @@
     <t>99120001070</t>
   </si>
   <si>
+    <t>99120001067</t>
+  </si>
+  <si>
+    <t>6 - 3</t>
+  </si>
+  <si>
+    <t>99120001071</t>
+  </si>
+  <si>
     <t>99120001069</t>
   </si>
   <si>
-    <t>6 - 3</t>
-  </si>
-  <si>
-    <t>99120001071</t>
-  </si>
-  <si>
-    <t>99120001067</t>
-  </si>
-  <si>
     <t>99120001065</t>
   </si>
   <si>
@@ -512,12 +512,12 @@
     <t>99120001079</t>
   </si>
   <si>
+    <t>99120001074</t>
+  </si>
+  <si>
     <t>99120001075</t>
   </si>
   <si>
-    <t>99120001074</t>
-  </si>
-  <si>
     <t>99120001078</t>
   </si>
   <si>
@@ -782,15 +782,15 @@
     <t>99120001146</t>
   </si>
   <si>
+    <t>99120001149</t>
+  </si>
+  <si>
+    <t>99120001150</t>
+  </si>
+  <si>
     <t>99120001148</t>
   </si>
   <si>
-    <t>99120001150</t>
-  </si>
-  <si>
-    <t>99120001149</t>
-  </si>
-  <si>
     <t>99120001151</t>
   </si>
   <si>
@@ -806,12 +806,12 @@
     <t>20</t>
   </si>
   <si>
+    <t>99120001154</t>
+  </si>
+  <si>
     <t>99120001160</t>
   </si>
   <si>
-    <t>99120001154</t>
-  </si>
-  <si>
     <t>99120001158</t>
   </si>
   <si>
@@ -821,12 +821,12 @@
     <t>99120001153</t>
   </si>
   <si>
+    <t>99120001156</t>
+  </si>
+  <si>
     <t>99120001159</t>
   </si>
   <si>
-    <t>99120001156</t>
-  </si>
-  <si>
     <t>99120001155</t>
   </si>
   <si>
@@ -848,12 +848,12 @@
     <t>99120001168</t>
   </si>
   <si>
+    <t>99120001164</t>
+  </si>
+  <si>
     <t>99120001167</t>
   </si>
   <si>
-    <t>99120001164</t>
-  </si>
-  <si>
     <t>99120001163</t>
   </si>
   <si>
@@ -878,15 +878,15 @@
     <t>99120001176</t>
   </si>
   <si>
+    <t>99120001174</t>
+  </si>
+  <si>
+    <t>99120001175</t>
+  </si>
+  <si>
     <t>99120001172</t>
   </si>
   <si>
-    <t>99120001174</t>
-  </si>
-  <si>
-    <t>99120001175</t>
-  </si>
-  <si>
     <t>99120001169</t>
   </si>
   <si>
@@ -983,18 +983,18 @@
     <t>99120001207</t>
   </si>
   <si>
+    <t>99120001206</t>
+  </si>
+  <si>
     <t>99120001208</t>
   </si>
   <si>
-    <t>99120001206</t>
+    <t>99120001202</t>
   </si>
   <si>
     <t>99120001204</t>
   </si>
   <si>
-    <t>99120001202</t>
-  </si>
-  <si>
     <t>99120001201</t>
   </si>
   <si>
@@ -1016,12 +1016,12 @@
     <t>99120001211</t>
   </si>
   <si>
+    <t>99120001210</t>
+  </si>
+  <si>
     <t>99120001216</t>
   </si>
   <si>
-    <t>99120001210</t>
-  </si>
-  <si>
     <t>99120001213</t>
   </si>
   <si>
@@ -1082,6 +1082,9 @@
     <t>30</t>
   </si>
   <si>
+    <t>99120001233</t>
+  </si>
+  <si>
     <t>99120001235</t>
   </si>
   <si>
@@ -1092,9 +1095,6 @@
   </si>
   <si>
     <t>99120001240</t>
-  </si>
-  <si>
-    <t>99120001233</t>
   </si>
   <si>
     <t>99120001234</t>
@@ -1520,7 +1520,7 @@
         <v>58</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H10" s="0" t="s">
         <v>63</v>
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H12" s="0" t="s">
         <v>69</v>
@@ -1654,22 +1654,22 @@
         <v>34</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F14" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="0" t="s">
+      <c r="I14" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="0" t="s">
         <v>75</v>
-      </c>
-      <c r="I14" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="0" t="s">
-        <v>76</v>
       </c>
       <c r="K14" s="0" t="s">
         <v>20</v>
@@ -1689,13 +1689,13 @@
         <v>34</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H15" s="0" t="s">
         <v>77</v>
@@ -1724,10 +1724,10 @@
         <v>56</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G16" s="0" t="s">
         <v>29</v>
@@ -1794,7 +1794,7 @@
         <v>28</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F18" s="0" t="s">
         <v>86</v>
@@ -1803,7 +1803,7 @@
         <v>16</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I18" s="0" t="s">
         <v>18</v>
@@ -1940,7 +1940,7 @@
         <v>86</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H22" s="0" t="s">
         <v>25</v>
@@ -2007,10 +2007,10 @@
         <v>35</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H24" s="0" t="s">
         <v>37</v>
@@ -2039,7 +2039,7 @@
         <v>56</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F25" s="0" t="s">
         <v>97</v>
@@ -2048,7 +2048,7 @@
         <v>52</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>18</v>
@@ -2074,7 +2074,7 @@
         <v>100</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>71</v>
@@ -2249,22 +2249,22 @@
         <v>34</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H31" s="0" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I31" s="0" t="s">
         <v>18</v>
       </c>
       <c r="J31" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K31" s="0" t="s">
         <v>20</v>
@@ -2284,16 +2284,16 @@
         <v>34</v>
       </c>
       <c r="E32" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="G32" s="0" t="s">
-        <v>35</v>
-      </c>
       <c r="H32" s="0" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="I32" s="0" t="s">
         <v>18</v>
@@ -2325,10 +2325,10 @@
         <v>86</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H33" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>18</v>
@@ -2360,7 +2360,7 @@
         <v>81</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H34" s="0" t="s">
         <v>82</v>
@@ -2389,7 +2389,7 @@
         <v>13</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F35" s="0" t="s">
         <v>113</v>
@@ -2398,7 +2398,7 @@
         <v>24</v>
       </c>
       <c r="H35" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I35" s="0" t="s">
         <v>18</v>
@@ -2459,16 +2459,16 @@
         <v>28</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F37" s="0" t="s">
         <v>68</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H37" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I37" s="0" t="s">
         <v>18</v>
@@ -2637,7 +2637,7 @@
         <v>52</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G42" s="0" t="s">
         <v>16</v>
@@ -2710,7 +2710,7 @@
         <v>124</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H44" s="0" t="s">
         <v>25</v>
@@ -2745,7 +2745,7 @@
         <v>71</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H45" s="0" t="s">
         <v>53</v>
@@ -2774,7 +2774,7 @@
         <v>34</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F46" s="0" t="s">
         <v>58</v>
@@ -2783,7 +2783,7 @@
         <v>29</v>
       </c>
       <c r="H46" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I46" s="0" t="s">
         <v>18</v>
@@ -2847,7 +2847,7 @@
         <v>35</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G48" s="0" t="s">
         <v>57</v>
@@ -2879,7 +2879,7 @@
         <v>49</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F49" s="0" t="s">
         <v>68</v>
@@ -2958,7 +2958,7 @@
         <v>52</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I51" s="0" t="s">
         <v>18</v>
@@ -2984,7 +2984,7 @@
         <v>28</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F52" s="0" t="s">
         <v>51</v>
@@ -3054,16 +3054,16 @@
         <v>34</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H54" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I54" s="0" t="s">
         <v>18</v>
@@ -3124,16 +3124,16 @@
         <v>49</v>
       </c>
       <c r="E56" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F56" s="0" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G56" s="0" t="s">
         <v>35</v>
       </c>
       <c r="H56" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I56" s="0" t="s">
         <v>18</v>
@@ -3197,10 +3197,10 @@
         <v>14</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H58" s="0" t="s">
         <v>17</v>
@@ -3270,7 +3270,7 @@
         <v>23</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H60" s="0" t="s">
         <v>69</v>
@@ -3299,7 +3299,7 @@
         <v>34</v>
       </c>
       <c r="E61" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F61" s="0" t="s">
         <v>23</v>
@@ -3308,7 +3308,7 @@
         <v>29</v>
       </c>
       <c r="H61" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I61" s="0" t="s">
         <v>18</v>
@@ -3439,7 +3439,7 @@
         <v>150</v>
       </c>
       <c r="E65" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F65" s="0" t="s">
         <v>15</v>
@@ -3448,7 +3448,7 @@
         <v>31</v>
       </c>
       <c r="H65" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I65" s="0" t="s">
         <v>18</v>
@@ -3483,7 +3483,7 @@
         <v>35</v>
       </c>
       <c r="H66" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I66" s="0" t="s">
         <v>18</v>
@@ -3509,13 +3509,13 @@
         <v>13</v>
       </c>
       <c r="E67" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F67" s="0" t="s">
         <v>71</v>
       </c>
       <c r="G67" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H67" s="0" t="s">
         <v>79</v>
@@ -3550,7 +3550,7 @@
         <v>97</v>
       </c>
       <c r="G68" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H68" s="0" t="s">
         <v>69</v>
@@ -3579,16 +3579,16 @@
         <v>13</v>
       </c>
       <c r="E69" s="0" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F69" s="0" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G69" s="0" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H69" s="0" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="I69" s="0" t="s">
         <v>18</v>
@@ -3649,16 +3649,16 @@
         <v>13</v>
       </c>
       <c r="E71" s="0" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H71" s="0" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="I71" s="0" t="s">
         <v>18</v>
@@ -3719,7 +3719,7 @@
         <v>150</v>
       </c>
       <c r="E73" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F73" s="0" t="s">
         <v>30</v>
@@ -3728,7 +3728,7 @@
         <v>57</v>
       </c>
       <c r="H73" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>18</v>
@@ -3792,7 +3792,7 @@
         <v>29</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G75" s="0" t="s">
         <v>16</v>
@@ -3830,7 +3830,7 @@
         <v>23</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H76" s="0" t="s">
         <v>63</v>
@@ -3859,16 +3859,16 @@
         <v>34</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F77" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H77" s="0" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I77" s="0" t="s">
         <v>18</v>
@@ -3894,16 +3894,16 @@
         <v>34</v>
       </c>
       <c r="E78" s="0" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F78" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="H78" s="0" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I78" s="0" t="s">
         <v>18</v>
@@ -3970,7 +3970,7 @@
         <v>58</v>
       </c>
       <c r="G80" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H80" s="0" t="s">
         <v>53</v>
@@ -3999,7 +3999,7 @@
         <v>49</v>
       </c>
       <c r="E81" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F81" s="0" t="s">
         <v>58</v>
@@ -4008,7 +4008,7 @@
         <v>52</v>
       </c>
       <c r="H81" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I81" s="0" t="s">
         <v>18</v>
@@ -4037,13 +4037,13 @@
         <v>31</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G82" s="0" t="s">
         <v>57</v>
       </c>
       <c r="H82" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I82" s="0" t="s">
         <v>18</v>
@@ -4069,7 +4069,7 @@
         <v>56</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F83" s="0" t="s">
         <v>71</v>
@@ -4078,7 +4078,7 @@
         <v>29</v>
       </c>
       <c r="H83" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>18</v>
@@ -4177,7 +4177,7 @@
         <v>24</v>
       </c>
       <c r="F86" s="0" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G86" s="0" t="s">
         <v>59</v>
@@ -4209,16 +4209,16 @@
         <v>56</v>
       </c>
       <c r="E87" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F87" s="0" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G87" s="0" t="s">
         <v>14</v>
       </c>
       <c r="H87" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I87" s="0" t="s">
         <v>18</v>
@@ -4250,7 +4250,7 @@
         <v>15</v>
       </c>
       <c r="G88" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H88" s="0" t="s">
         <v>25</v>
@@ -4279,10 +4279,10 @@
         <v>56</v>
       </c>
       <c r="E89" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F89" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G89" s="0" t="s">
         <v>16</v>
@@ -4320,7 +4320,7 @@
         <v>181</v>
       </c>
       <c r="G90" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H90" s="0" t="s">
         <v>82</v>
@@ -4454,7 +4454,7 @@
         <v>34</v>
       </c>
       <c r="E94" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F94" s="0" t="s">
         <v>181</v>
@@ -4495,7 +4495,7 @@
         <v>181</v>
       </c>
       <c r="G95" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H95" s="0" t="s">
         <v>63</v>
@@ -4530,7 +4530,7 @@
         <v>181</v>
       </c>
       <c r="G96" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H96" s="0" t="s">
         <v>60</v>
@@ -4600,7 +4600,7 @@
         <v>68</v>
       </c>
       <c r="G98" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H98" s="0" t="s">
         <v>72</v>
@@ -4629,16 +4629,16 @@
         <v>13</v>
       </c>
       <c r="E99" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F99" s="0" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G99" s="0" t="s">
         <v>22</v>
       </c>
       <c r="H99" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I99" s="0" t="s">
         <v>18</v>
@@ -4670,7 +4670,7 @@
         <v>51</v>
       </c>
       <c r="G100" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H100" s="0" t="s">
         <v>53</v>
@@ -4743,7 +4743,7 @@
         <v>36</v>
       </c>
       <c r="H102" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I102" s="0" t="s">
         <v>18</v>
@@ -4769,16 +4769,16 @@
         <v>34</v>
       </c>
       <c r="E103" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F103" s="0" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G103" s="0" t="s">
         <v>14</v>
       </c>
       <c r="H103" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>18</v>
@@ -4842,7 +4842,7 @@
         <v>57</v>
       </c>
       <c r="F105" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G105" s="0" t="s">
         <v>16</v>
@@ -4874,16 +4874,16 @@
         <v>56</v>
       </c>
       <c r="E106" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F106" s="0" t="s">
         <v>201</v>
       </c>
       <c r="G106" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H106" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I106" s="0" t="s">
         <v>18</v>
@@ -4912,7 +4912,7 @@
         <v>59</v>
       </c>
       <c r="F107" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G107" s="0" t="s">
         <v>52</v>
@@ -4979,7 +4979,7 @@
         <v>13</v>
       </c>
       <c r="E109" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F109" s="0" t="s">
         <v>15</v>
@@ -5087,7 +5087,7 @@
         <v>22</v>
       </c>
       <c r="F112" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G112" s="0" t="s">
         <v>31</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="G113" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H113" s="0" t="s">
         <v>66</v>
@@ -5160,7 +5160,7 @@
         <v>113</v>
       </c>
       <c r="G114" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H114" s="0" t="s">
         <v>53</v>
@@ -5192,7 +5192,7 @@
         <v>29</v>
       </c>
       <c r="F115" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G115" s="0" t="s">
         <v>36</v>
@@ -5230,10 +5230,10 @@
         <v>97</v>
       </c>
       <c r="G116" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H116" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I116" s="0" t="s">
         <v>18</v>
@@ -5294,7 +5294,7 @@
         <v>34</v>
       </c>
       <c r="E118" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F118" s="0" t="s">
         <v>88</v>
@@ -5303,7 +5303,7 @@
         <v>59</v>
       </c>
       <c r="H118" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I118" s="0" t="s">
         <v>18</v>
@@ -5332,7 +5332,7 @@
         <v>57</v>
       </c>
       <c r="F119" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G119" s="0" t="s">
         <v>14</v>
@@ -5364,7 +5364,7 @@
         <v>49</v>
       </c>
       <c r="E120" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F120" s="0" t="s">
         <v>58</v>
@@ -5373,7 +5373,7 @@
         <v>16</v>
       </c>
       <c r="H120" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I120" s="0" t="s">
         <v>18</v>
@@ -5434,7 +5434,7 @@
         <v>56</v>
       </c>
       <c r="E122" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F122" s="0" t="s">
         <v>88</v>
@@ -5443,7 +5443,7 @@
         <v>14</v>
       </c>
       <c r="H122" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I122" s="0" t="s">
         <v>18</v>
@@ -5475,7 +5475,7 @@
         <v>51</v>
       </c>
       <c r="G123" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H123" s="0" t="s">
         <v>82</v>
@@ -5507,10 +5507,10 @@
         <v>52</v>
       </c>
       <c r="F124" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G124" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H124" s="0" t="s">
         <v>72</v>
@@ -5644,7 +5644,7 @@
         <v>34</v>
       </c>
       <c r="E128" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F128" s="0" t="s">
         <v>229</v>
@@ -5653,7 +5653,7 @@
         <v>50</v>
       </c>
       <c r="H128" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I128" s="0" t="s">
         <v>18</v>
@@ -5688,7 +5688,7 @@
         <v>24</v>
       </c>
       <c r="H129" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I129" s="0" t="s">
         <v>18</v>
@@ -5749,7 +5749,7 @@
         <v>56</v>
       </c>
       <c r="E131" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F131" s="0" t="s">
         <v>86</v>
@@ -5758,7 +5758,7 @@
         <v>35</v>
       </c>
       <c r="H131" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I131" s="0" t="s">
         <v>18</v>
@@ -5784,16 +5784,16 @@
         <v>100</v>
       </c>
       <c r="E132" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F132" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G132" s="0" t="s">
         <v>59</v>
       </c>
       <c r="H132" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I132" s="0" t="s">
         <v>18</v>
@@ -5889,7 +5889,7 @@
         <v>28</v>
       </c>
       <c r="E135" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F135" s="0" t="s">
         <v>68</v>
@@ -5930,7 +5930,7 @@
         <v>58</v>
       </c>
       <c r="G136" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H136" s="0" t="s">
         <v>17</v>
@@ -6070,7 +6070,7 @@
         <v>58</v>
       </c>
       <c r="G140" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H140" s="0" t="s">
         <v>37</v>
@@ -6099,16 +6099,16 @@
         <v>28</v>
       </c>
       <c r="E141" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F141" s="0" t="s">
         <v>246</v>
       </c>
       <c r="G141" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H141" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I141" s="0" t="s">
         <v>18</v>
@@ -6172,10 +6172,10 @@
         <v>57</v>
       </c>
       <c r="F143" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G143" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H143" s="0" t="s">
         <v>60</v>
@@ -6213,7 +6213,7 @@
         <v>14</v>
       </c>
       <c r="H144" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I144" s="0" t="s">
         <v>18</v>
@@ -6242,7 +6242,7 @@
         <v>52</v>
       </c>
       <c r="F145" s="0" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G145" s="0" t="s">
         <v>29</v>
@@ -6312,7 +6312,7 @@
         <v>14</v>
       </c>
       <c r="F147" s="0" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G147" s="0" t="s">
         <v>29</v>
@@ -6344,16 +6344,16 @@
         <v>34</v>
       </c>
       <c r="E148" s="0" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F148" s="0" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="G148" s="0" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H148" s="0" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>18</v>
@@ -6414,16 +6414,16 @@
         <v>34</v>
       </c>
       <c r="E150" s="0" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F150" s="0" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="G150" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H150" s="0" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I150" s="0" t="s">
         <v>18</v>
@@ -6455,7 +6455,7 @@
         <v>15</v>
       </c>
       <c r="G151" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H151" s="0" t="s">
         <v>66</v>
@@ -6484,7 +6484,7 @@
         <v>34</v>
       </c>
       <c r="E152" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F152" s="0" t="s">
         <v>260</v>
@@ -6493,7 +6493,7 @@
         <v>22</v>
       </c>
       <c r="H152" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>18</v>
@@ -6519,7 +6519,7 @@
         <v>49</v>
       </c>
       <c r="E153" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F153" s="0" t="s">
         <v>148</v>
@@ -6554,16 +6554,16 @@
         <v>56</v>
       </c>
       <c r="E154" s="0" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F154" s="0" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="G154" s="0" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="H154" s="0" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="I154" s="0" t="s">
         <v>18</v>
@@ -6589,16 +6589,16 @@
         <v>56</v>
       </c>
       <c r="E155" s="0" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="F155" s="0" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="G155" s="0" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="H155" s="0" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I155" s="0" t="s">
         <v>18</v>
@@ -6624,7 +6624,7 @@
         <v>222</v>
       </c>
       <c r="E156" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F156" s="0" t="s">
         <v>58</v>
@@ -6633,7 +6633,7 @@
         <v>16</v>
       </c>
       <c r="H156" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>18</v>
@@ -6697,13 +6697,13 @@
         <v>31</v>
       </c>
       <c r="F158" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G158" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H158" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I158" s="0" t="s">
         <v>18</v>
@@ -6729,16 +6729,16 @@
         <v>34</v>
       </c>
       <c r="E159" s="0" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="F159" s="0" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="G159" s="0" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H159" s="0" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>18</v>
@@ -6764,16 +6764,16 @@
         <v>34</v>
       </c>
       <c r="E160" s="0" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="F160" s="0" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="G160" s="0" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="H160" s="0" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I160" s="0" t="s">
         <v>18</v>
@@ -6834,13 +6834,13 @@
         <v>13</v>
       </c>
       <c r="E162" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F162" s="0" t="s">
         <v>23</v>
       </c>
       <c r="G162" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H162" s="0" t="s">
         <v>79</v>
@@ -6939,16 +6939,16 @@
         <v>34</v>
       </c>
       <c r="E165" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F165" s="0" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G165" s="0" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H165" s="0" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="I165" s="0" t="s">
         <v>18</v>
@@ -6974,16 +6974,16 @@
         <v>34</v>
       </c>
       <c r="E166" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F166" s="0" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G166" s="0" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H166" s="0" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>18</v>
@@ -7047,7 +7047,7 @@
         <v>52</v>
       </c>
       <c r="F168" s="0" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="G168" s="0" t="s">
         <v>57</v>
@@ -7082,10 +7082,10 @@
         <v>59</v>
       </c>
       <c r="F169" s="0" t="s">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="G169" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H169" s="0" t="s">
         <v>82</v>
@@ -7117,7 +7117,7 @@
         <v>57</v>
       </c>
       <c r="F170" s="0" t="s">
-        <v>181</v>
+        <v>40</v>
       </c>
       <c r="G170" s="0" t="s">
         <v>35</v>
@@ -7152,7 +7152,7 @@
         <v>29</v>
       </c>
       <c r="F171" s="0" t="s">
-        <v>181</v>
+        <v>40</v>
       </c>
       <c r="G171" s="0" t="s">
         <v>24</v>
@@ -7187,10 +7187,10 @@
         <v>22</v>
       </c>
       <c r="F172" s="0" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="G172" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H172" s="0" t="s">
         <v>25</v>
@@ -7219,16 +7219,16 @@
         <v>28</v>
       </c>
       <c r="E173" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F173" s="0" t="s">
-        <v>181</v>
+        <v>58</v>
       </c>
       <c r="G173" s="0" t="s">
         <v>52</v>
       </c>
       <c r="H173" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I173" s="0" t="s">
         <v>18</v>
@@ -7254,16 +7254,16 @@
         <v>34</v>
       </c>
       <c r="E174" s="0" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F174" s="0" t="s">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="G174" s="0" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H174" s="0" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I174" s="0" t="s">
         <v>18</v>
@@ -7289,16 +7289,16 @@
         <v>34</v>
       </c>
       <c r="E175" s="0" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F175" s="0" t="s">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="G175" s="0" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="H175" s="0" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I175" s="0" t="s">
         <v>18</v>
@@ -7324,16 +7324,16 @@
         <v>34</v>
       </c>
       <c r="E176" s="0" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F176" s="0" t="s">
-        <v>181</v>
+        <v>81</v>
       </c>
       <c r="G176" s="0" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H176" s="0" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I176" s="0" t="s">
         <v>18</v>
@@ -7362,13 +7362,13 @@
         <v>31</v>
       </c>
       <c r="F177" s="0" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="G177" s="0" t="s">
         <v>59</v>
       </c>
       <c r="H177" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I177" s="0" t="s">
         <v>18</v>
@@ -7403,7 +7403,7 @@
         <v>16</v>
       </c>
       <c r="H178" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>18</v>
@@ -7470,7 +7470,7 @@
         <v>181</v>
       </c>
       <c r="G180" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H180" s="0" t="s">
         <v>69</v>
@@ -7569,7 +7569,7 @@
         <v>34</v>
       </c>
       <c r="E183" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F183" s="0" t="s">
         <v>181</v>
@@ -7578,7 +7578,7 @@
         <v>57</v>
       </c>
       <c r="H183" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I183" s="0" t="s">
         <v>18</v>
@@ -7604,7 +7604,7 @@
         <v>49</v>
       </c>
       <c r="E184" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F184" s="0" t="s">
         <v>181</v>
@@ -7645,7 +7645,7 @@
         <v>181</v>
       </c>
       <c r="G185" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H185" s="0" t="s">
         <v>37</v>
@@ -7715,7 +7715,7 @@
         <v>181</v>
       </c>
       <c r="G187" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H187" s="0" t="s">
         <v>32</v>
@@ -7814,7 +7814,7 @@
         <v>34</v>
       </c>
       <c r="E190" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F190" s="0" t="s">
         <v>181</v>
@@ -7823,7 +7823,7 @@
         <v>31</v>
       </c>
       <c r="H190" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I190" s="0" t="s">
         <v>18</v>
@@ -7884,16 +7884,16 @@
         <v>34</v>
       </c>
       <c r="E192" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F192" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G192" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H192" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>18</v>
@@ -8024,16 +8024,16 @@
         <v>21</v>
       </c>
       <c r="E196" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F196" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G196" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H196" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>18</v>
@@ -8068,7 +8068,7 @@
         <v>22</v>
       </c>
       <c r="H197" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>18</v>
@@ -8170,7 +8170,7 @@
         <v>181</v>
       </c>
       <c r="G200" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H200" s="0" t="s">
         <v>63</v>
@@ -8199,7 +8199,7 @@
         <v>49</v>
       </c>
       <c r="E201" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F201" s="0" t="s">
         <v>181</v>
@@ -8208,7 +8208,7 @@
         <v>50</v>
       </c>
       <c r="H201" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I201" s="0" t="s">
         <v>18</v>
@@ -8240,7 +8240,7 @@
         <v>181</v>
       </c>
       <c r="G202" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H202" s="0" t="s">
         <v>32</v>
@@ -8339,16 +8339,16 @@
         <v>34</v>
       </c>
       <c r="E205" s="0" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F205" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G205" s="0" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H205" s="0" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="I205" s="0" t="s">
         <v>18</v>
@@ -8374,16 +8374,16 @@
         <v>34</v>
       </c>
       <c r="E206" s="0" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F206" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G206" s="0" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H206" s="0" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="I206" s="0" t="s">
         <v>18</v>
@@ -8409,16 +8409,16 @@
         <v>34</v>
       </c>
       <c r="E207" s="0" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="F207" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G207" s="0" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="H207" s="0" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
       <c r="I207" s="0" t="s">
         <v>18</v>
@@ -8444,16 +8444,16 @@
         <v>34</v>
       </c>
       <c r="E208" s="0" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F208" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="I208" s="0" t="s">
         <v>18</v>
@@ -8619,7 +8619,7 @@
         <v>21</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F213" s="0" t="s">
         <v>181</v>
@@ -8628,7 +8628,7 @@
         <v>36</v>
       </c>
       <c r="H213" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I213" s="0" t="s">
         <v>18</v>
@@ -8660,7 +8660,7 @@
         <v>181</v>
       </c>
       <c r="G214" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H214" s="0" t="s">
         <v>32</v>
@@ -8689,16 +8689,16 @@
         <v>34</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F215" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I215" s="0" t="s">
         <v>18</v>
@@ -8724,16 +8724,16 @@
         <v>34</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F216" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I216" s="0" t="s">
         <v>18</v>
@@ -8765,7 +8765,7 @@
         <v>181</v>
       </c>
       <c r="G217" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H217" s="0" t="s">
         <v>60</v>
@@ -8870,7 +8870,7 @@
         <v>181</v>
       </c>
       <c r="G220" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H220" s="0" t="s">
         <v>72</v>
@@ -8908,7 +8908,7 @@
         <v>29</v>
       </c>
       <c r="H221" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I221" s="0" t="s">
         <v>18</v>
@@ -8934,7 +8934,7 @@
         <v>34</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F222" s="0" t="s">
         <v>181</v>
@@ -8943,7 +8943,7 @@
         <v>50</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I222" s="0" t="s">
         <v>18</v>
@@ -9010,7 +9010,7 @@
         <v>181</v>
       </c>
       <c r="G224" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H224" s="0" t="s">
         <v>66</v>
@@ -9039,7 +9039,7 @@
         <v>56</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F225" s="0" t="s">
         <v>181</v>
@@ -9109,7 +9109,7 @@
         <v>13</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F227" s="0" t="s">
         <v>181</v>
@@ -9118,7 +9118,7 @@
         <v>59</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I227" s="0" t="s">
         <v>18</v>
@@ -9144,7 +9144,7 @@
         <v>21</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F228" s="0" t="s">
         <v>181</v>
@@ -9153,7 +9153,7 @@
         <v>24</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I228" s="0" t="s">
         <v>18</v>
@@ -9255,7 +9255,7 @@
         <v>181</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H231" s="0" t="s">
         <v>32</v>
@@ -9325,7 +9325,7 @@
         <v>181</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H233" s="0" t="s">
         <v>17</v>
@@ -9354,16 +9354,16 @@
         <v>34</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="F234" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="I234" s="0" t="s">
         <v>18</v>
@@ -9389,16 +9389,16 @@
         <v>34</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="F235" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I235" s="0" t="s">
         <v>18</v>
@@ -9424,16 +9424,16 @@
         <v>34</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F236" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I236" s="0" t="s">
         <v>18</v>
@@ -9459,16 +9459,16 @@
         <v>34</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F237" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I237" s="0" t="s">
         <v>18</v>
@@ -9494,16 +9494,16 @@
         <v>34</v>
       </c>
       <c r="E238" s="0" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F238" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G238" s="0" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="H238" s="0" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="I238" s="0" t="s">
         <v>18</v>
@@ -9535,10 +9535,10 @@
         <v>181</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I239" s="0" t="s">
         <v>18</v>
@@ -9564,7 +9564,7 @@
         <v>34</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F240" s="0" t="s">
         <v>181</v>
@@ -9599,16 +9599,16 @@
         <v>34</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F241" s="0" t="s">
         <v>181</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I241" s="0" t="s">
         <v>18</v>
